--- a/data_meta/hoaglands_recipes_p_v1.xlsx
+++ b/data_meta/hoaglands_recipes_p_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monik\Documents\git\2025_g34p\meta_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monik\Documents\git\2025_g34p\data_meta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315CCD24-BAEA-468A-A5EE-00E5AD604077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602989E9-7682-4AF3-A974-58D7A5BCB6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{5A275A07-A470-45D3-A544-9A609AEF5A01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{5A275A07-A470-45D3-A544-9A609AEF5A01}"/>
   </bookViews>
   <sheets>
     <sheet name="recipes_v1" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2727" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2727" uniqueCount="163">
   <si>
     <t>Primary N addition compounds</t>
   </si>
@@ -1884,9 +1884,6 @@
     <t>3.3% reduction</t>
   </si>
   <si>
-    <t>mL for 0.675 L</t>
-  </si>
-  <si>
     <t>uL for 0.675 L</t>
   </si>
   <si>
@@ -2598,6 +2595,12 @@
       </rPr>
       <t>4</t>
     </r>
+  </si>
+  <si>
+    <t>mL for 7 L</t>
+  </si>
+  <si>
+    <t>mL for 7</t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3339,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3508,7 +3511,6 @@
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3551,61 +3553,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -25887,10 +25881,10 @@
         <v>128</v>
       </c>
       <c r="Y5" s="123" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z5" s="123" t="s">
         <v>141</v>
-      </c>
-      <c r="Z5" s="123" t="s">
-        <v>142</v>
       </c>
       <c r="AB5" s="46" t="s">
         <v>1</v>
@@ -25993,8 +25987,8 @@
         <v>20</v>
       </c>
       <c r="Y6">
-        <f>U6*0.675</f>
-        <v>0.67500000000000004</v>
+        <f>U6*7</f>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>675</v>
@@ -26104,8 +26098,8 @@
         <v>40</v>
       </c>
       <c r="Y7">
-        <f t="shared" ref="Y7:Y18" si="6">U7*0.675</f>
-        <v>1.35</v>
+        <f>U7*7</f>
+        <v>14</v>
       </c>
       <c r="Z7">
         <v>1350</v>
@@ -26130,7 +26124,7 @@
         <v>130</v>
       </c>
       <c r="AH7">
-        <f t="shared" ref="AH7:AH9" si="7">AE7*20</f>
+        <f t="shared" ref="AH7:AH9" si="6">AE7*20</f>
         <v>40</v>
       </c>
       <c r="AJ7" s="14" t="s">
@@ -26214,8 +26208,8 @@
         <v>30</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="6"/>
-        <v>1.0125000000000002</v>
+        <f>U8*7</f>
+        <v>10.5</v>
       </c>
       <c r="Z8">
         <v>1012.5</v>
@@ -26240,7 +26234,7 @@
         <v>131</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="AJ8" s="14" t="s">
@@ -26325,8 +26319,8 @@
         <v>40</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="6"/>
-        <v>1.35</v>
+        <f>U9*7</f>
+        <v>14</v>
       </c>
       <c r="Z9">
         <v>1350</v>
@@ -26351,7 +26345,7 @@
         <v>132</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="AJ9" s="14" t="s">
@@ -26489,7 +26483,7 @@
         <v>128</v>
       </c>
       <c r="Y12" s="123" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="Z12" s="123"/>
       <c r="AB12" s="46" t="s">
@@ -26592,7 +26586,7 @@
         <v>0</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="6"/>
+        <f>U13*7</f>
         <v>0</v>
       </c>
       <c r="Z13">
@@ -26645,14 +26639,14 @@
         <v>0</v>
       </c>
       <c r="F14" s="33">
-        <f t="shared" ref="F14:F16" si="8">IF(OR(C14=0, E14=0), 0, (D14*1000)/(1000/(C14*E14)))</f>
+        <f t="shared" ref="F14:F16" si="7">IF(OR(C14=0, E14=0), 0, (D14*1000)/(1000/(C14*E14)))</f>
         <v>0</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>134</v>
       </c>
       <c r="H14">
-        <f t="shared" ref="H14:H18" si="9">E14*20</f>
+        <f t="shared" ref="H14:H18" si="8">E14*20</f>
         <v>0</v>
       </c>
       <c r="J14" s="94" t="s">
@@ -26668,14 +26662,14 @@
         <v>0</v>
       </c>
       <c r="N14" s="33">
-        <f t="shared" ref="N14:N16" si="10">IF(OR(K14=0, M14=0), 0, (L14*1000)/(1000/(K14*M14)))</f>
+        <f t="shared" ref="N14:N16" si="9">IF(OR(K14=0, M14=0), 0, (L14*1000)/(1000/(K14*M14)))</f>
         <v>0</v>
       </c>
       <c r="O14" s="35" t="s">
         <v>134</v>
       </c>
       <c r="P14">
-        <f t="shared" ref="P14:P18" si="11">M14*20</f>
+        <f t="shared" ref="P14:P18" si="10">M14*20</f>
         <v>0</v>
       </c>
       <c r="R14" s="94" t="s">
@@ -26697,11 +26691,11 @@
         <v>134</v>
       </c>
       <c r="X14" s="35">
-        <f t="shared" ref="X14:X18" si="12">U14*20</f>
+        <f t="shared" ref="X14:X18" si="11">U14*20</f>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="6"/>
+        <f>U14*7</f>
         <v>0</v>
       </c>
       <c r="Z14">
@@ -26720,14 +26714,14 @@
         <v>0</v>
       </c>
       <c r="AF14" s="33">
-        <f t="shared" ref="AF14:AF16" si="13">IF(OR(AC14=0, AE14=0), 0, (AD14*1000)/(1000/(AC14*AE14)))</f>
+        <f t="shared" ref="AF14:AF16" si="12">IF(OR(AC14=0, AE14=0), 0, (AD14*1000)/(1000/(AC14*AE14)))</f>
         <v>0</v>
       </c>
       <c r="AG14" s="35" t="s">
         <v>134</v>
       </c>
       <c r="AH14" s="35">
-        <f t="shared" ref="AH14:AH18" si="14">AE14*20</f>
+        <f t="shared" ref="AH14:AH18" si="13">AE14*20</f>
         <v>0</v>
       </c>
       <c r="AJ14" s="65" t="s">
@@ -26750,14 +26744,14 @@
         <v>0.04</v>
       </c>
       <c r="F15" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4.0034799999999997</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>135</v>
       </c>
       <c r="H15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="J15" s="95" t="s">
@@ -26773,14 +26767,14 @@
         <v>0.5</v>
       </c>
       <c r="N15" s="33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>50.043500000000002</v>
       </c>
       <c r="O15" s="35" t="s">
         <v>135</v>
       </c>
       <c r="P15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="R15" s="95" t="s">
@@ -26802,12 +26796,12 @@
         <v>135</v>
       </c>
       <c r="X15" s="35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="6"/>
-        <v>0.67500000000000004</v>
+        <f>U15*7</f>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>675</v>
@@ -26825,14 +26819,14 @@
         <v>0.8</v>
       </c>
       <c r="AF15" s="33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>80.069599999999994</v>
       </c>
       <c r="AG15" s="35" t="s">
         <v>135</v>
       </c>
       <c r="AH15" s="35">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>16</v>
       </c>
       <c r="AJ15" s="14" t="s">
@@ -26859,14 +26853,14 @@
         <v>1</v>
       </c>
       <c r="F16" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>492.96</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>136</v>
       </c>
       <c r="H16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="J16" s="96" t="s">
@@ -26882,42 +26876,42 @@
         <v>1</v>
       </c>
       <c r="N16" s="33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>492.96</v>
       </c>
       <c r="O16" s="35" t="s">
         <v>136</v>
       </c>
       <c r="P16">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="R16" s="96" t="s">
+        <v>108</v>
+      </c>
+      <c r="S16" s="22">
+        <v>2</v>
+      </c>
+      <c r="T16" s="22">
+        <v>246.48</v>
+      </c>
+      <c r="U16" s="22">
+        <v>1</v>
+      </c>
+      <c r="V16" s="33">
+        <f t="shared" ref="V16:V18" si="14">(T16*1000)/(1000/(S16*U16))</f>
+        <v>492.96</v>
+      </c>
+      <c r="W16" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="X16" s="35">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="R16" s="96" t="s">
-        <v>108</v>
-      </c>
-      <c r="S16" s="22">
-        <v>2</v>
-      </c>
-      <c r="T16" s="22">
-        <v>246.48</v>
-      </c>
-      <c r="U16" s="22">
-        <v>1</v>
-      </c>
-      <c r="V16" s="33">
-        <f t="shared" ref="V16:V18" si="15">(T16*1000)/(1000/(S16*U16))</f>
-        <v>492.96</v>
-      </c>
-      <c r="W16" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="X16" s="35">
-        <f t="shared" si="12"/>
-        <v>20</v>
-      </c>
       <c r="Y16">
-        <f t="shared" si="6"/>
-        <v>0.67500000000000004</v>
+        <f>U16*7</f>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>675</v>
@@ -26935,14 +26929,14 @@
         <v>1</v>
       </c>
       <c r="AF16" s="33">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>492.96</v>
       </c>
       <c r="AG16" s="35" t="s">
         <v>136</v>
       </c>
       <c r="AH16" s="35">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="AJ16" s="14" t="s">
@@ -26971,7 +26965,7 @@
         <v>137</v>
       </c>
       <c r="H17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="J17" s="29" t="s">
@@ -26989,33 +26983,33 @@
         <v>137</v>
       </c>
       <c r="P17">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="R17" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="S17" s="22">
+        <v>1</v>
+      </c>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22">
+        <v>1</v>
+      </c>
+      <c r="V17" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="X17" s="35">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="R17" s="29" t="s">
+      <c r="Y17">
+        <f>U17*7</f>
         <v>7</v>
-      </c>
-      <c r="S17" s="22">
-        <v>1</v>
-      </c>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22">
-        <v>1</v>
-      </c>
-      <c r="V17" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="X17" s="35">
-        <f t="shared" si="12"/>
-        <v>20</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="6"/>
-        <v>0.67500000000000004</v>
       </c>
       <c r="Z17">
         <v>675</v>
@@ -27035,7 +27029,7 @@
         <v>137</v>
       </c>
       <c r="AH17" s="35">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="AJ17" s="14" t="s">
@@ -27060,14 +27054,14 @@
         <v>1</v>
       </c>
       <c r="F18" s="33">
-        <f t="shared" ref="F18" si="16">(D18*1000)/(1000/(C18*E18))</f>
+        <f t="shared" ref="F18" si="15">(D18*1000)/(1000/(C18*E18))</f>
         <v>0</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>138</v>
       </c>
       <c r="H18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="J18" s="29" t="s">
@@ -27081,40 +27075,40 @@
         <v>1</v>
       </c>
       <c r="N18" s="33">
-        <f t="shared" ref="N18" si="17">(L18*1000)/(1000/(K18*M18))</f>
+        <f t="shared" ref="N18" si="16">(L18*1000)/(1000/(K18*M18))</f>
         <v>0</v>
       </c>
       <c r="O18" s="35" t="s">
         <v>138</v>
       </c>
       <c r="P18">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="R18" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="22">
+        <v>1</v>
+      </c>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22">
+        <v>1</v>
+      </c>
+      <c r="V18" s="33">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="X18" s="35">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="R18" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="22">
-        <v>1</v>
-      </c>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22">
-        <v>1</v>
-      </c>
-      <c r="V18" s="33">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="X18" s="35">
-        <f t="shared" si="12"/>
-        <v>20</v>
-      </c>
       <c r="Y18">
-        <f t="shared" si="6"/>
-        <v>0.67500000000000004</v>
+        <f>U18*7</f>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>675</v>
@@ -27130,14 +27124,14 @@
         <v>1</v>
       </c>
       <c r="AF18" s="33">
-        <f t="shared" ref="AF18" si="18">(AD18*1000)/(1000/(AC18*AE18))</f>
+        <f t="shared" ref="AF18" si="17">(AD18*1000)/(1000/(AC18*AE18))</f>
         <v>0</v>
       </c>
       <c r="AG18" s="35" t="s">
         <v>138</v>
       </c>
       <c r="AH18" s="35">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="AJ18" s="14" t="s">
@@ -27305,7 +27299,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="52">
-        <f t="shared" ref="F22:F35" si="19">IF(OR(C22=0, E22=0), 0, (D22*1000)/(1000/(C22*E22)))</f>
+        <f t="shared" ref="F22:F35" si="18">IF(OR(C22=0, E22=0), 0, (D22*1000)/(1000/(C22*E22)))</f>
         <v>0</v>
       </c>
       <c r="G22" s="35"/>
@@ -27398,7 +27392,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G23" s="35"/>
@@ -27418,7 +27412,7 @@
         <v>0.5</v>
       </c>
       <c r="N23" s="33">
-        <f t="shared" ref="N23:N35" si="20">IF(OR(K23=0, M23=0), 0, (L23*1000)/(1000/(K23*M23)))</f>
+        <f t="shared" ref="N23:N35" si="19">IF(OR(K23=0, M23=0), 0, (L23*1000)/(1000/(K23*M23)))</f>
         <v>15.48685</v>
       </c>
       <c r="O23" s="35"/>
@@ -27438,7 +27432,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="33">
-        <f t="shared" ref="V23:V35" si="21">IF(OR(S23=0,U23=0),0,(T23*1000)/(1000/(S23*U23)))</f>
+        <f t="shared" ref="V23:V35" si="20">IF(OR(S23=0,U23=0),0,(T23*1000)/(1000/(S23*U23)))</f>
         <v>30.973700000000001</v>
       </c>
       <c r="W23" s="35"/>
@@ -27460,7 +27454,7 @@
         <v>2</v>
       </c>
       <c r="AF23" s="33">
-        <f t="shared" ref="AF23:AF35" si="22">IF(OR(AC23=0,AE23=0),0,(AD23*1000)/(1000/(AC23*AE23)))</f>
+        <f t="shared" ref="AF23:AF35" si="21">IF(OR(AC23=0,AE23=0),0,(AD23*1000)/(1000/(AC23*AE23)))</f>
         <v>61.947400000000002</v>
       </c>
       <c r="AG23" s="35"/>
@@ -27489,7 +27483,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>156.37719999999999</v>
       </c>
       <c r="G24" s="35"/>
@@ -27509,7 +27503,7 @@
         <v>2</v>
       </c>
       <c r="N24" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>156.37719999999999</v>
       </c>
       <c r="O24" s="35"/>
@@ -27529,7 +27523,7 @@
         <v>2</v>
       </c>
       <c r="V24" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>156.37719999999999</v>
       </c>
       <c r="W24" s="35"/>
@@ -27551,7 +27545,7 @@
         <v>2</v>
       </c>
       <c r="AF24" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>156.37719999999999</v>
       </c>
       <c r="AG24" s="35"/>
@@ -27582,7 +27576,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>56.024000000000001</v>
       </c>
       <c r="G25" s="35"/>
@@ -27602,7 +27596,7 @@
         <v>2</v>
       </c>
       <c r="N25" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>56.024000000000001</v>
       </c>
       <c r="O25" s="35"/>
@@ -27622,7 +27616,7 @@
         <v>2</v>
       </c>
       <c r="V25" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>56.024000000000001</v>
       </c>
       <c r="W25" s="35"/>
@@ -27644,7 +27638,7 @@
         <v>2</v>
       </c>
       <c r="AF25" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>56.024000000000001</v>
       </c>
       <c r="AG25" s="35"/>
@@ -27675,7 +27669,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>160.31200000000001</v>
       </c>
       <c r="G26" s="35"/>
@@ -27695,7 +27689,7 @@
         <v>1.75</v>
       </c>
       <c r="N26" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>140.273</v>
       </c>
       <c r="O26" s="35"/>
@@ -27715,7 +27709,7 @@
         <v>1.5</v>
       </c>
       <c r="V26" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>120.23400000000001</v>
       </c>
       <c r="W26" s="35"/>
@@ -27737,7 +27731,7 @@
         <v>1.6</v>
       </c>
       <c r="AF26" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>128.24959999999999</v>
       </c>
       <c r="AG26" s="35"/>
@@ -27768,7 +27762,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>112.048</v>
       </c>
       <c r="G27" s="35"/>
@@ -27788,7 +27782,7 @@
         <v>1.75</v>
       </c>
       <c r="N27" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>98.042000000000002</v>
       </c>
       <c r="O27" s="35"/>
@@ -27808,7 +27802,7 @@
         <v>1.5</v>
       </c>
       <c r="V27" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>84.036000000000001</v>
       </c>
       <c r="W27" s="35"/>
@@ -27830,7 +27824,7 @@
         <v>1.6</v>
       </c>
       <c r="AF27" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>89.638400000000004</v>
       </c>
       <c r="AG27" s="35"/>
@@ -27875,7 +27869,7 @@
         <v>1.75</v>
       </c>
       <c r="N28" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>49.021000000000001</v>
       </c>
       <c r="O28" s="35"/>
@@ -27895,7 +27889,7 @@
         <v>2</v>
       </c>
       <c r="V28" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>56.024000000000001</v>
       </c>
       <c r="W28" s="35"/>
@@ -27948,7 +27942,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G29" s="35"/>
@@ -27968,7 +27962,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O29" s="35"/>
@@ -27988,7 +27982,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W29" s="35"/>
@@ -28010,7 +28004,7 @@
         <v>0</v>
       </c>
       <c r="AF29" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG29" s="35"/>
@@ -28041,7 +28035,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G30" s="35"/>
@@ -28061,7 +28055,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O30" s="35"/>
@@ -28081,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W30" s="35"/>
@@ -28103,7 +28097,7 @@
         <v>0</v>
       </c>
       <c r="AF30" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG30" s="35"/>
@@ -28134,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G31" s="35"/>
@@ -28154,7 +28148,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O31" s="35"/>
@@ -28174,7 +28168,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W31" s="35"/>
@@ -28196,7 +28190,7 @@
         <v>0</v>
       </c>
       <c r="AF31" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG31" s="35"/>
@@ -28227,7 +28221,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G32" s="35"/>
@@ -28247,7 +28241,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O32" s="35"/>
@@ -28267,7 +28261,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W32" s="35"/>
@@ -28289,7 +28283,7 @@
         <v>0</v>
       </c>
       <c r="AF32" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AG32" s="35"/>
@@ -28320,7 +28314,7 @@
         <v>0.04</v>
       </c>
       <c r="F33" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1.6031200000000001</v>
       </c>
       <c r="G33" s="35"/>
@@ -28340,7 +28334,7 @@
         <v>0.5</v>
       </c>
       <c r="N33" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>20.039000000000001</v>
       </c>
       <c r="O33" s="35"/>
@@ -28360,7 +28354,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>40.078000000000003</v>
       </c>
       <c r="W33" s="35"/>
@@ -28382,7 +28376,7 @@
         <v>0.8</v>
       </c>
       <c r="AF33" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>32.062399999999997</v>
       </c>
       <c r="AG33" s="35"/>
@@ -28413,7 +28407,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>48.61</v>
       </c>
       <c r="G34" s="35"/>
@@ -28433,7 +28427,7 @@
         <v>1</v>
       </c>
       <c r="N34" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>48.61</v>
       </c>
       <c r="O34" s="35"/>
@@ -28453,7 +28447,7 @@
         <v>1</v>
       </c>
       <c r="V34" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>48.61</v>
       </c>
       <c r="W34" s="35"/>
@@ -28475,7 +28469,7 @@
         <v>1</v>
       </c>
       <c r="AF34" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>48.61</v>
       </c>
       <c r="AG34" s="35"/>
@@ -28500,7 +28494,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>64.13</v>
       </c>
       <c r="G35" s="35"/>
@@ -28520,7 +28514,7 @@
         <v>1</v>
       </c>
       <c r="N35" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>64.13</v>
       </c>
       <c r="O35" s="35"/>
@@ -28540,7 +28534,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="33">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>64.13</v>
       </c>
       <c r="W35" s="35"/>
@@ -28562,7 +28556,7 @@
         <v>1</v>
       </c>
       <c r="AF35" s="33">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>64.13</v>
       </c>
       <c r="AG35" s="35"/>
@@ -28723,7 +28717,7 @@
         <v>210.09000000000003</v>
       </c>
       <c r="M39" s="35">
-        <f t="shared" ref="M39:M44" si="23">C48-K39</f>
+        <f t="shared" ref="M39:M44" si="22">C48-K39</f>
         <v>0</v>
       </c>
       <c r="N39" s="32">
@@ -28737,7 +28731,7 @@
         <v>210.09</v>
       </c>
       <c r="U39" s="118">
-        <f t="shared" ref="U39:U44" si="24">S39-C48</f>
+        <f t="shared" ref="U39:U44" si="23">S39-C48</f>
         <v>0</v>
       </c>
       <c r="V39" s="32">
@@ -28751,7 +28745,7 @@
         <v>210.09</v>
       </c>
       <c r="AE39" s="35">
-        <f t="shared" ref="AE39:AE44" si="25">C48-AC39</f>
+        <f t="shared" ref="AE39:AE44" si="24">C48-AC39</f>
         <v>0</v>
       </c>
       <c r="AF39" s="32">
@@ -28767,7 +28761,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="35">
-        <f t="shared" ref="E40:E44" si="26">C49-C40</f>
+        <f t="shared" ref="E40:E44" si="25">C49-C40</f>
         <v>30.973700000000001</v>
       </c>
       <c r="F40" s="32"/>
@@ -28779,7 +28773,7 @@
         <v>15.48685</v>
       </c>
       <c r="M40" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>15.48685</v>
       </c>
       <c r="N40" s="32"/>
@@ -28791,7 +28785,7 @@
         <v>30.973700000000001</v>
       </c>
       <c r="U40" s="118">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V40" s="32"/>
@@ -28803,7 +28797,7 @@
         <v>61.947400000000002</v>
       </c>
       <c r="AE40" s="35">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-30.973700000000001</v>
       </c>
       <c r="AF40" s="32"/>
@@ -28817,7 +28811,7 @@
         <v>156.37719999999999</v>
       </c>
       <c r="E41" s="35">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F41" s="32"/>
@@ -28829,7 +28823,7 @@
         <v>156.37719999999999</v>
       </c>
       <c r="M41" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N41" s="32"/>
@@ -28841,7 +28835,7 @@
         <v>156.37719999999999</v>
       </c>
       <c r="U41" s="118">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V41" s="32"/>
@@ -28853,7 +28847,7 @@
         <v>156.37719999999999</v>
       </c>
       <c r="AE41" s="35">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AF41" s="32"/>
@@ -28867,7 +28861,7 @@
         <v>161.91512</v>
       </c>
       <c r="E42" s="35">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-1.6031199999999899</v>
       </c>
       <c r="F42" s="32"/>
@@ -28879,7 +28873,7 @@
         <v>160.31200000000001</v>
       </c>
       <c r="M42" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N42" s="32"/>
@@ -28891,7 +28885,7 @@
         <v>160.31200000000001</v>
       </c>
       <c r="U42" s="118">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V42" s="32"/>
@@ -28903,7 +28897,7 @@
         <v>160.31199999999998</v>
       </c>
       <c r="AE42" s="35">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AF42" s="32"/>
@@ -28917,7 +28911,7 @@
         <v>48.61</v>
       </c>
       <c r="E43" s="35">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F43" s="32"/>
@@ -28929,7 +28923,7 @@
         <v>48.61</v>
       </c>
       <c r="M43" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N43" s="32"/>
@@ -28941,7 +28935,7 @@
         <v>48.61</v>
       </c>
       <c r="U43" s="118">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V43" s="32"/>
@@ -28953,7 +28947,7 @@
         <v>48.61</v>
       </c>
       <c r="AE43" s="35">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AF43" s="32"/>
@@ -28968,7 +28962,7 @@
       </c>
       <c r="D44" s="36"/>
       <c r="E44" s="35">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F44" s="38"/>
@@ -28981,7 +28975,7 @@
       </c>
       <c r="L44" s="36"/>
       <c r="M44" s="35">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N44" s="38"/>
@@ -28994,7 +28988,7 @@
       </c>
       <c r="T44" s="36"/>
       <c r="U44" s="118">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V44" s="38"/>
@@ -29007,7 +29001,7 @@
       </c>
       <c r="AD44" s="36"/>
       <c r="AE44" s="35">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AF44" s="38"/>
@@ -29067,7 +29061,7 @@
         <v>151.27000000000001</v>
       </c>
       <c r="U49">
-        <f t="shared" ref="U49:U52" si="27">S41-S49</f>
+        <f t="shared" ref="U49:U52" si="26">S41-S49</f>
         <v>5.1071999999999775</v>
       </c>
     </row>
@@ -29085,7 +29079,7 @@
         <v>155.08000000000001</v>
       </c>
       <c r="U50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>5.2319999999999993</v>
       </c>
     </row>
@@ -29103,7 +29097,7 @@
         <v>47.02</v>
       </c>
       <c r="U51">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1.5899999999999963</v>
       </c>
     </row>
@@ -29121,7 +29115,7 @@
         <v>62.04</v>
       </c>
       <c r="U52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>2.0899999999999963</v>
       </c>
     </row>
@@ -29154,22 +29148,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" style="172" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
     <col min="4" max="6" width="0" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="4.85546875" customWidth="1"/>
     <col min="8" max="8" width="11.5703125" customWidth="1"/>
     <col min="9" max="9" width="7.140625" customWidth="1"/>
-    <col min="10" max="10" width="29.28515625" style="172" customWidth="1"/>
+    <col min="10" max="10" width="29.28515625" customWidth="1"/>
     <col min="12" max="14" width="0" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="4.85546875" customWidth="1"/>
     <col min="16" max="16" width="11.7109375" customWidth="1"/>
     <col min="17" max="17" width="7.140625" customWidth="1"/>
-    <col min="18" max="18" width="29.28515625" style="172" customWidth="1"/>
+    <col min="18" max="18" width="29.28515625" customWidth="1"/>
     <col min="20" max="22" width="0" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="3.5703125" customWidth="1"/>
     <col min="24" max="24" width="11.140625" customWidth="1"/>
     <col min="25" max="25" width="7.140625" customWidth="1"/>
-    <col min="26" max="26" width="29.28515625" style="172" customWidth="1"/>
+    <col min="26" max="26" width="29.28515625" customWidth="1"/>
     <col min="28" max="28" width="13" hidden="1" customWidth="1"/>
     <col min="29" max="30" width="0" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="3.5703125" customWidth="1"/>
@@ -29183,45 +29177,45 @@
       <c r="I1" s="111"/>
     </row>
     <row r="2" spans="2:36" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="169" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="143"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="142"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="202" t="s">
+      <c r="J2" s="195" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="160"/>
-      <c r="L2" s="160"/>
-      <c r="M2" s="160"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="162"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="161"/>
       <c r="Q2" s="4"/>
-      <c r="R2" s="202" t="s">
+      <c r="R2" s="195" t="s">
         <v>89</v>
       </c>
-      <c r="S2" s="160"/>
-      <c r="T2" s="160"/>
-      <c r="U2" s="160"/>
-      <c r="V2" s="161"/>
-      <c r="W2" s="160"/>
-      <c r="X2" s="162"/>
+      <c r="S2" s="159"/>
+      <c r="T2" s="159"/>
+      <c r="U2" s="159"/>
+      <c r="V2" s="160"/>
+      <c r="W2" s="159"/>
+      <c r="X2" s="161"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="202" t="s">
+      <c r="Z2" s="195" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" s="160"/>
-      <c r="AB2" s="160"/>
-      <c r="AC2" s="160"/>
-      <c r="AD2" s="161"/>
-      <c r="AE2" s="160"/>
-      <c r="AF2" s="162"/>
+      <c r="AA2" s="159"/>
+      <c r="AB2" s="159"/>
+      <c r="AC2" s="159"/>
+      <c r="AD2" s="160"/>
+      <c r="AE2" s="159"/>
+      <c r="AF2" s="161"/>
       <c r="AH2" s="7" t="s">
         <v>88</v>
       </c>
@@ -29229,37 +29223,37 @@
       <c r="AJ2" s="9"/>
     </row>
     <row r="3" spans="2:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="174"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="145"/>
-      <c r="H3" s="147"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="146"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="146"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="147"/>
+      <c r="J3" s="196"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="145"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="146"/>
       <c r="Q3" s="3"/>
-      <c r="R3" s="204"/>
-      <c r="S3" s="166"/>
-      <c r="T3" s="167"/>
-      <c r="U3" s="167"/>
+      <c r="R3" s="197"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
       <c r="V3" s="28"/>
-      <c r="W3" s="167"/>
-      <c r="X3" s="168"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="165"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="204"/>
-      <c r="AA3" s="166"/>
-      <c r="AB3" s="167"/>
-      <c r="AC3" s="167"/>
+      <c r="Z3" s="197"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
       <c r="AD3" s="28"/>
-      <c r="AE3" s="167"/>
-      <c r="AF3" s="168"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="165"/>
       <c r="AH3" s="65" t="s">
         <v>23</v>
       </c>
@@ -29271,45 +29265,45 @@
       </c>
     </row>
     <row r="4" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B4" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="148"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="151"/>
+      <c r="B4" s="171" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="147"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="150"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="175" t="s">
+      <c r="J4" s="171" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="148"/>
-      <c r="L4" s="149"/>
-      <c r="M4" s="149"/>
-      <c r="N4" s="150"/>
-      <c r="O4" s="149"/>
-      <c r="P4" s="151"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="148"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="150"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="175" t="s">
+      <c r="R4" s="171" t="s">
         <v>21</v>
       </c>
-      <c r="S4" s="148"/>
-      <c r="T4" s="149"/>
-      <c r="U4" s="149"/>
-      <c r="V4" s="150"/>
-      <c r="W4" s="149"/>
-      <c r="X4" s="151"/>
+      <c r="S4" s="147"/>
+      <c r="T4" s="148"/>
+      <c r="U4" s="148"/>
+      <c r="V4" s="149"/>
+      <c r="W4" s="148"/>
+      <c r="X4" s="150"/>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="175" t="s">
+      <c r="Z4" s="171" t="s">
         <v>21</v>
       </c>
-      <c r="AA4" s="148"/>
-      <c r="AB4" s="149"/>
-      <c r="AC4" s="149"/>
-      <c r="AD4" s="150"/>
-      <c r="AE4" s="149"/>
-      <c r="AF4" s="151"/>
+      <c r="AA4" s="147"/>
+      <c r="AB4" s="148"/>
+      <c r="AC4" s="148"/>
+      <c r="AD4" s="149"/>
+      <c r="AE4" s="148"/>
+      <c r="AF4" s="150"/>
       <c r="AH4" s="14" t="s">
         <v>56</v>
       </c>
@@ -29321,80 +29315,80 @@
       </c>
     </row>
     <row r="5" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B5" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="139" t="s">
+      <c r="B5" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="139" t="s">
+      <c r="D5" s="123" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="139" t="s">
+      <c r="E5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="140" t="s">
+      <c r="F5" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="139"/>
-      <c r="H5" s="152" t="s">
+      <c r="G5" s="123"/>
+      <c r="H5" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="J5" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="139" t="s">
+      <c r="J5" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="139" t="s">
+      <c r="L5" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="M5" s="139" t="s">
+      <c r="M5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="140" t="s">
+      <c r="N5" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="O5" s="139"/>
-      <c r="P5" s="152" t="s">
+      <c r="O5" s="123"/>
+      <c r="P5" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="R5" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="139" t="s">
+      <c r="R5" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="T5" s="139" t="s">
+      <c r="T5" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="U5" s="139" t="s">
+      <c r="U5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="V5" s="140" t="s">
+      <c r="V5" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="W5" s="139"/>
-      <c r="X5" s="152" t="s">
+      <c r="W5" s="123"/>
+      <c r="X5" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="Z5" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="139" t="s">
+      <c r="Z5" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="AB5" s="139" t="s">
+      <c r="AB5" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="AC5" s="139" t="s">
+      <c r="AC5" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="AD5" s="140" t="s">
+      <c r="AD5" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="AE5" s="139"/>
-      <c r="AF5" s="152" t="s">
+      <c r="AE5" s="123"/>
+      <c r="AF5" s="151" t="s">
         <v>128</v>
       </c>
       <c r="AH5" s="14" t="s">
@@ -29409,31 +29403,31 @@
       </c>
     </row>
     <row r="6" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B6" s="177" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="153">
-        <v>1</v>
-      </c>
-      <c r="D6" s="153">
+      <c r="B6" s="173" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="152">
+        <v>1</v>
+      </c>
+      <c r="D6" s="152">
         <v>115.3</v>
       </c>
-      <c r="E6" s="153">
-        <v>0</v>
-      </c>
-      <c r="F6" s="153">
+      <c r="E6" s="152">
+        <v>0</v>
+      </c>
+      <c r="F6" s="152">
         <f t="shared" ref="F6:F8" si="0">IF(OR(D6=0,E6=0),0,(D6*1000)/(1000/(C6*E6)))</f>
         <v>0</v>
       </c>
-      <c r="G6" s="153" t="s">
+      <c r="G6" s="152" t="s">
         <v>129</v>
       </c>
-      <c r="H6" s="163">
+      <c r="H6" s="162">
         <f>E6*20</f>
         <v>0</v>
       </c>
-      <c r="J6" s="205" t="s">
-        <v>143</v>
+      <c r="J6" s="198" t="s">
+        <v>142</v>
       </c>
       <c r="K6" s="133">
         <v>1</v>
@@ -29451,12 +29445,12 @@
       <c r="O6" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="P6" s="155">
+      <c r="P6" s="154">
         <f>M6*20</f>
         <v>10</v>
       </c>
-      <c r="R6" s="205" t="s">
-        <v>143</v>
+      <c r="R6" s="198" t="s">
+        <v>142</v>
       </c>
       <c r="S6" s="133">
         <v>1</v>
@@ -29474,12 +29468,12 @@
       <c r="W6" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="X6" s="155">
+      <c r="X6" s="154">
         <f>U6*20</f>
         <v>20</v>
       </c>
-      <c r="Z6" s="205" t="s">
-        <v>143</v>
+      <c r="Z6" s="198" t="s">
+        <v>142</v>
       </c>
       <c r="AA6" s="133">
         <v>1</v>
@@ -29497,7 +29491,7 @@
       <c r="AE6" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="AF6" s="155">
+      <c r="AF6" s="154">
         <f>AC6*20</f>
         <v>40</v>
       </c>
@@ -29513,31 +29507,31 @@
       </c>
     </row>
     <row r="7" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B7" s="178" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="153">
-        <v>2</v>
-      </c>
-      <c r="D7" s="153">
+      <c r="B7" s="174" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="152">
+        <v>2</v>
+      </c>
+      <c r="D7" s="152">
         <v>101.1</v>
       </c>
-      <c r="E7" s="153">
-        <v>2</v>
-      </c>
-      <c r="F7" s="153">
+      <c r="E7" s="152">
+        <v>2</v>
+      </c>
+      <c r="F7" s="152">
         <f t="shared" si="0"/>
         <v>404.4</v>
       </c>
-      <c r="G7" s="153" t="s">
+      <c r="G7" s="152" t="s">
         <v>130</v>
       </c>
-      <c r="H7" s="163">
+      <c r="H7" s="162">
         <f>E7*20</f>
         <v>40</v>
       </c>
-      <c r="J7" s="206" t="s">
-        <v>144</v>
+      <c r="J7" s="199" t="s">
+        <v>143</v>
       </c>
       <c r="K7" s="133">
         <v>2</v>
@@ -29555,12 +29549,12 @@
       <c r="O7" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="P7" s="155">
+      <c r="P7" s="154">
         <f t="shared" ref="P7:P9" si="4">M7*20</f>
         <v>40</v>
       </c>
-      <c r="R7" s="206" t="s">
-        <v>144</v>
+      <c r="R7" s="199" t="s">
+        <v>143</v>
       </c>
       <c r="S7" s="133">
         <v>2</v>
@@ -29578,12 +29572,12 @@
       <c r="W7" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="X7" s="155">
+      <c r="X7" s="154">
         <f t="shared" ref="X7:X9" si="5">U7*20</f>
         <v>40</v>
       </c>
-      <c r="Z7" s="206" t="s">
-        <v>144</v>
+      <c r="Z7" s="199" t="s">
+        <v>143</v>
       </c>
       <c r="AA7" s="133">
         <v>2</v>
@@ -29601,7 +29595,7 @@
       <c r="AE7" s="133" t="s">
         <v>130</v>
       </c>
-      <c r="AF7" s="155">
+      <c r="AF7" s="154">
         <f t="shared" ref="AF7:AF9" si="6">AC7*20</f>
         <v>40</v>
       </c>
@@ -29616,31 +29610,31 @@
       </c>
     </row>
     <row r="8" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B8" s="179" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="153">
-        <v>2</v>
-      </c>
-      <c r="D8" s="153">
+      <c r="B8" s="175" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="152">
+        <v>2</v>
+      </c>
+      <c r="D8" s="152">
         <v>164.08799999999999</v>
       </c>
-      <c r="E8" s="153">
-        <v>2</v>
-      </c>
-      <c r="F8" s="153">
+      <c r="E8" s="152">
+        <v>2</v>
+      </c>
+      <c r="F8" s="152">
         <f t="shared" si="0"/>
         <v>656.35199999999998</v>
       </c>
-      <c r="G8" s="153" t="s">
+      <c r="G8" s="152" t="s">
         <v>131</v>
       </c>
-      <c r="H8" s="163">
+      <c r="H8" s="162">
         <f>E8*20</f>
         <v>40</v>
       </c>
-      <c r="J8" s="207" t="s">
-        <v>145</v>
+      <c r="J8" s="200" t="s">
+        <v>144</v>
       </c>
       <c r="K8" s="133">
         <v>2</v>
@@ -29658,12 +29652,12 @@
       <c r="O8" s="133" t="s">
         <v>131</v>
       </c>
-      <c r="P8" s="155">
+      <c r="P8" s="154">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="R8" s="207" t="s">
-        <v>145</v>
+      <c r="R8" s="200" t="s">
+        <v>144</v>
       </c>
       <c r="S8" s="133">
         <v>2</v>
@@ -29681,12 +29675,12 @@
       <c r="W8" s="133" t="s">
         <v>131</v>
       </c>
-      <c r="X8" s="155">
+      <c r="X8" s="154">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="Z8" s="207" t="s">
-        <v>145</v>
+      <c r="Z8" s="200" t="s">
+        <v>144</v>
       </c>
       <c r="AA8" s="133">
         <v>2</v>
@@ -29704,7 +29698,7 @@
       <c r="AE8" s="133" t="s">
         <v>131</v>
       </c>
-      <c r="AF8" s="155">
+      <c r="AF8" s="154">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
@@ -29720,95 +29714,95 @@
       </c>
     </row>
     <row r="9" spans="2:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="180" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="164">
-        <v>1</v>
-      </c>
-      <c r="D9" s="164">
+      <c r="B9" s="176" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="163">
+        <v>1</v>
+      </c>
+      <c r="D9" s="163">
         <v>80.043000000000006</v>
       </c>
-      <c r="E9" s="164">
+      <c r="E9" s="163">
         <v>1.5</v>
       </c>
-      <c r="F9" s="164">
+      <c r="F9" s="163">
         <f>IF(OR(D9=0,E9=0),0,(D9*1000)/(1000/(C9*E9)))</f>
         <v>120.06450000000001</v>
       </c>
-      <c r="G9" s="164" t="s">
+      <c r="G9" s="163" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="165">
+      <c r="H9" s="164">
         <f>E9*20</f>
         <v>30</v>
       </c>
-      <c r="J9" s="208" t="s">
-        <v>146</v>
-      </c>
-      <c r="K9" s="156">
-        <v>1</v>
-      </c>
-      <c r="L9" s="156">
+      <c r="J9" s="201" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" s="155">
+        <v>1</v>
+      </c>
+      <c r="L9" s="155">
         <v>80.043000000000006</v>
       </c>
-      <c r="M9" s="156">
+      <c r="M9" s="155">
         <v>1.75</v>
       </c>
-      <c r="N9" s="156">
+      <c r="N9" s="155">
         <f>IF(OR(L9=0,M9=0),0,(L9*1000)/(1000/(K9*M9)))</f>
         <v>140.07524999999998</v>
       </c>
-      <c r="O9" s="156" t="s">
+      <c r="O9" s="155" t="s">
         <v>132</v>
       </c>
-      <c r="P9" s="158">
+      <c r="P9" s="157">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="R9" s="208" t="s">
-        <v>146</v>
-      </c>
-      <c r="S9" s="156">
-        <v>1</v>
-      </c>
-      <c r="T9" s="156">
+      <c r="R9" s="201" t="s">
+        <v>145</v>
+      </c>
+      <c r="S9" s="155">
+        <v>1</v>
+      </c>
+      <c r="T9" s="155">
         <v>80.043000000000006</v>
       </c>
-      <c r="U9" s="156">
-        <v>2</v>
-      </c>
-      <c r="V9" s="156">
+      <c r="U9" s="155">
+        <v>2</v>
+      </c>
+      <c r="V9" s="155">
         <f>IF(OR(T9=0,U9=0),0,(T9*1000)/(1000/(S9*U9)))</f>
         <v>160.08600000000001</v>
       </c>
-      <c r="W9" s="156" t="s">
+      <c r="W9" s="155" t="s">
         <v>132</v>
       </c>
-      <c r="X9" s="158">
+      <c r="X9" s="157">
         <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="Z9" s="208" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA9" s="156">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="156">
+      <c r="Z9" s="201" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA9" s="155">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="155">
         <v>80.043000000000006</v>
       </c>
-      <c r="AC9" s="156">
+      <c r="AC9" s="155">
         <v>1.3</v>
       </c>
-      <c r="AD9" s="156">
+      <c r="AD9" s="155">
         <f>IF(OR(AB9=0,AC9=0),0,(AB9*1000)/(1000/(AA9*AC9)))</f>
         <v>104.05590000000001</v>
       </c>
-      <c r="AE9" s="156" t="s">
+      <c r="AE9" s="155" t="s">
         <v>132</v>
       </c>
-      <c r="AF9" s="158">
+      <c r="AF9" s="157">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
@@ -29823,42 +29817,42 @@
       </c>
     </row>
     <row r="10" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B10" s="175" t="s">
+      <c r="B10" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="149"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="159"/>
-      <c r="J10" s="176" t="s">
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
+      <c r="F10" s="149"/>
+      <c r="G10" s="148"/>
+      <c r="H10" s="158"/>
+      <c r="J10" s="172" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="139"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="139"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="139"/>
-      <c r="P10" s="209"/>
-      <c r="R10" s="175" t="s">
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="139"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="202"/>
+      <c r="R10" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="S10" s="149"/>
-      <c r="T10" s="149"/>
-      <c r="U10" s="149"/>
-      <c r="V10" s="150"/>
-      <c r="W10" s="149"/>
-      <c r="X10" s="151"/>
-      <c r="Z10" s="175" t="s">
+      <c r="S10" s="148"/>
+      <c r="T10" s="148"/>
+      <c r="U10" s="148"/>
+      <c r="V10" s="149"/>
+      <c r="W10" s="148"/>
+      <c r="X10" s="150"/>
+      <c r="Z10" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="AA10" s="149"/>
-      <c r="AB10" s="149"/>
-      <c r="AC10" s="149"/>
-      <c r="AD10" s="150"/>
-      <c r="AE10" s="149"/>
-      <c r="AF10" s="151"/>
+      <c r="AA10" s="148"/>
+      <c r="AB10" s="148"/>
+      <c r="AC10" s="148"/>
+      <c r="AD10" s="149"/>
+      <c r="AE10" s="148"/>
+      <c r="AF10" s="150"/>
       <c r="AH10" s="14" t="s">
         <v>66</v>
       </c>
@@ -29870,80 +29864,80 @@
       </c>
     </row>
     <row r="11" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B11" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="139" t="s">
+      <c r="B11" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="139" t="s">
+      <c r="D11" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="139" t="s">
+      <c r="E11" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="140" t="s">
+      <c r="F11" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="139"/>
-      <c r="H11" s="152" t="s">
+      <c r="G11" s="123"/>
+      <c r="H11" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="J11" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="139" t="s">
+      <c r="J11" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="139" t="s">
+      <c r="L11" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="139" t="s">
+      <c r="M11" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="N11" s="140" t="s">
+      <c r="N11" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="O11" s="139"/>
-      <c r="P11" s="152" t="s">
+      <c r="O11" s="123"/>
+      <c r="P11" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="R11" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="139" t="s">
+      <c r="R11" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="T11" s="139" t="s">
+      <c r="T11" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="U11" s="139" t="s">
+      <c r="U11" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="V11" s="140" t="s">
+      <c r="V11" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="W11" s="139"/>
-      <c r="X11" s="152" t="s">
+      <c r="W11" s="123"/>
+      <c r="X11" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="Z11" s="176" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="139" t="s">
+      <c r="Z11" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="AB11" s="139" t="s">
+      <c r="AB11" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="139" t="s">
+      <c r="AC11" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="AD11" s="140" t="s">
+      <c r="AD11" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="AE11" s="139"/>
-      <c r="AF11" s="152" t="s">
+      <c r="AE11" s="123"/>
+      <c r="AF11" s="151" t="s">
         <v>128</v>
       </c>
       <c r="AH11" s="14" t="s">
@@ -29958,8 +29952,8 @@
       </c>
     </row>
     <row r="12" spans="2:36" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="181" t="s">
-        <v>147</v>
+      <c r="B12" s="177" t="s">
+        <v>146</v>
       </c>
       <c r="C12" s="133">
         <v>1</v>
@@ -29970,18 +29964,18 @@
       <c r="E12" s="133">
         <v>0</v>
       </c>
-      <c r="F12" s="154">
+      <c r="F12" s="153">
         <f>IF(OR(C12=0, E12=0), 0, (D12*1000)/(1000/(C12*E12)))</f>
         <v>0</v>
       </c>
-      <c r="G12" s="154" t="s">
+      <c r="G12" s="153" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="155">
-        <f>E12*20</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="181" t="s">
+      <c r="H12" s="154">
+        <f t="shared" ref="H12:H17" si="7">E12*20</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="177" t="s">
         <v>106</v>
       </c>
       <c r="K12" s="133">
@@ -29993,18 +29987,18 @@
       <c r="M12" s="133">
         <v>0</v>
       </c>
-      <c r="N12" s="154">
+      <c r="N12" s="153">
         <f>IF(OR(K12=0, M12=0), 0, (L12*1000)/(1000/(K12*M12)))</f>
         <v>0</v>
       </c>
-      <c r="O12" s="154" t="s">
+      <c r="O12" s="153" t="s">
         <v>133</v>
       </c>
-      <c r="P12" s="155">
+      <c r="P12" s="154">
         <f>M12*20</f>
         <v>0</v>
       </c>
-      <c r="R12" s="181" t="s">
+      <c r="R12" s="177" t="s">
         <v>106</v>
       </c>
       <c r="S12" s="133">
@@ -30016,17 +30010,17 @@
       <c r="U12" s="133">
         <v>0</v>
       </c>
-      <c r="V12" s="154">
-        <v>0</v>
-      </c>
-      <c r="W12" s="154" t="s">
+      <c r="V12" s="153">
+        <v>0</v>
+      </c>
+      <c r="W12" s="153" t="s">
         <v>133</v>
       </c>
-      <c r="X12" s="170">
+      <c r="X12" s="167">
         <f>U12*20</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="181" t="s">
+      <c r="Z12" s="177" t="s">
         <v>106</v>
       </c>
       <c r="AA12" s="133">
@@ -30038,14 +30032,14 @@
       <c r="AC12" s="133">
         <v>0</v>
       </c>
-      <c r="AD12" s="154">
+      <c r="AD12" s="153">
         <f>IF(OR(AA12=0, AC12=0), 0, (AB12*1000)/(1000/(AA12*AC12)))</f>
         <v>0</v>
       </c>
-      <c r="AE12" s="154" t="s">
+      <c r="AE12" s="153" t="s">
         <v>133</v>
       </c>
-      <c r="AF12" s="170">
+      <c r="AF12" s="167">
         <f>AC12*20</f>
         <v>0</v>
       </c>
@@ -30060,7 +30054,7 @@
       </c>
     </row>
     <row r="13" spans="2:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="182" t="s">
+      <c r="B13" s="178" t="s">
         <v>103</v>
       </c>
       <c r="C13" s="133">
@@ -30072,18 +30066,18 @@
       <c r="E13" s="133">
         <v>0</v>
       </c>
-      <c r="F13" s="154">
-        <f t="shared" ref="F13:F15" si="7">IF(OR(C13=0, E13=0), 0, (D13*1000)/(1000/(C13*E13)))</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="154" t="s">
+      <c r="F13" s="153">
+        <f t="shared" ref="F13:F15" si="8">IF(OR(C13=0, E13=0), 0, (D13*1000)/(1000/(C13*E13)))</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="H13" s="155">
-        <f>E13*20</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="182" t="s">
+      <c r="H13" s="154">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="178" t="s">
         <v>103</v>
       </c>
       <c r="K13" s="133">
@@ -30095,18 +30089,18 @@
       <c r="M13" s="133">
         <v>0</v>
       </c>
-      <c r="N13" s="154">
-        <f t="shared" ref="N13:N15" si="8">IF(OR(K13=0, M13=0), 0, (L13*1000)/(1000/(K13*M13)))</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="154" t="s">
+      <c r="N13" s="153">
+        <f t="shared" ref="N13:N15" si="9">IF(OR(K13=0, M13=0), 0, (L13*1000)/(1000/(K13*M13)))</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="P13" s="155">
-        <f t="shared" ref="P13:P17" si="9">M13*20</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="182" t="s">
+      <c r="P13" s="154">
+        <f t="shared" ref="P13:P17" si="10">M13*20</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="178" t="s">
         <v>103</v>
       </c>
       <c r="S13" s="133">
@@ -30118,17 +30112,17 @@
       <c r="U13" s="133">
         <v>0</v>
       </c>
-      <c r="V13" s="154">
-        <v>0</v>
-      </c>
-      <c r="W13" s="154" t="s">
+      <c r="V13" s="153">
+        <v>0</v>
+      </c>
+      <c r="W13" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="X13" s="170">
-        <f t="shared" ref="X13:X17" si="10">U13*20</f>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="182" t="s">
+      <c r="X13" s="167">
+        <f t="shared" ref="X13:X17" si="11">U13*20</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="178" t="s">
         <v>103</v>
       </c>
       <c r="AA13" s="133">
@@ -30140,15 +30134,15 @@
       <c r="AC13" s="133">
         <v>0</v>
       </c>
-      <c r="AD13" s="154">
-        <f t="shared" ref="AD13:AD15" si="11">IF(OR(AA13=0, AC13=0), 0, (AB13*1000)/(1000/(AA13*AC13)))</f>
-        <v>0</v>
-      </c>
-      <c r="AE13" s="154" t="s">
+      <c r="AD13" s="153">
+        <f t="shared" ref="AD13:AD15" si="12">IF(OR(AA13=0, AC13=0), 0, (AB13*1000)/(1000/(AA13*AC13)))</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="AF13" s="170">
-        <f t="shared" ref="AF13:AF17" si="12">AC13*20</f>
+      <c r="AF13" s="167">
+        <f t="shared" ref="AF13:AF17" si="13">AC13*20</f>
         <v>0</v>
       </c>
       <c r="AH13" s="65" t="s">
@@ -30158,8 +30152,8 @@
       <c r="AJ13" s="69"/>
     </row>
     <row r="14" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B14" s="183" t="s">
-        <v>148</v>
+      <c r="B14" s="179" t="s">
+        <v>147</v>
       </c>
       <c r="C14" s="133">
         <v>1</v>
@@ -30170,18 +30164,18 @@
       <c r="E14" s="133">
         <v>0.04</v>
       </c>
-      <c r="F14" s="154">
+      <c r="F14" s="153">
+        <f t="shared" si="8"/>
+        <v>4.0034799999999997</v>
+      </c>
+      <c r="G14" s="153" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="154">
         <f t="shared" si="7"/>
-        <v>4.0034799999999997</v>
-      </c>
-      <c r="G14" s="154" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="155">
-        <f>E14*20</f>
         <v>0.8</v>
       </c>
-      <c r="J14" s="183" t="s">
+      <c r="J14" s="179" t="s">
         <v>107</v>
       </c>
       <c r="K14" s="133">
@@ -30193,18 +30187,18 @@
       <c r="M14" s="133">
         <v>0.5</v>
       </c>
-      <c r="N14" s="154">
-        <f t="shared" si="8"/>
+      <c r="N14" s="153">
+        <f t="shared" si="9"/>
         <v>50.043500000000002</v>
       </c>
-      <c r="O14" s="154" t="s">
+      <c r="O14" s="153" t="s">
         <v>135</v>
       </c>
-      <c r="P14" s="155">
-        <f t="shared" si="9"/>
+      <c r="P14" s="154">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="R14" s="183" t="s">
+      <c r="R14" s="179" t="s">
         <v>107</v>
       </c>
       <c r="S14" s="133">
@@ -30216,97 +30210,97 @@
       <c r="U14" s="133">
         <v>1</v>
       </c>
-      <c r="V14" s="154">
-        <v>0</v>
-      </c>
-      <c r="W14" s="154" t="s">
+      <c r="V14" s="153">
+        <v>0</v>
+      </c>
+      <c r="W14" s="153" t="s">
         <v>135</v>
       </c>
-      <c r="X14" s="170">
+      <c r="X14" s="167">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="Z14" s="179" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA14" s="133">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="133">
+        <v>100.087</v>
+      </c>
+      <c r="AC14" s="166">
+        <v>0.8</v>
+      </c>
+      <c r="AD14" s="153">
+        <f t="shared" si="12"/>
+        <v>80.069599999999994</v>
+      </c>
+      <c r="AE14" s="153" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF14" s="167">
+        <f t="shared" si="13"/>
+        <v>16</v>
+      </c>
+      <c r="AH14" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI14" s="20">
+        <v>197.92</v>
+      </c>
+      <c r="AJ14" s="16">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="15" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="B15" s="180" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="133">
+        <v>2</v>
+      </c>
+      <c r="D15" s="133">
+        <v>246.48</v>
+      </c>
+      <c r="E15" s="133">
+        <v>1</v>
+      </c>
+      <c r="F15" s="153">
+        <f t="shared" si="8"/>
+        <v>492.96</v>
+      </c>
+      <c r="G15" s="153" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15" s="154">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="J15" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="133">
+        <v>2</v>
+      </c>
+      <c r="L15" s="133">
+        <v>246.48</v>
+      </c>
+      <c r="M15" s="133">
+        <v>1</v>
+      </c>
+      <c r="N15" s="153">
+        <f t="shared" si="9"/>
+        <v>492.96</v>
+      </c>
+      <c r="O15" s="153" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="154">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="Z14" s="183" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA14" s="133">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="133">
-        <v>100.087</v>
-      </c>
-      <c r="AC14" s="169">
-        <v>0.8</v>
-      </c>
-      <c r="AD14" s="154">
-        <f t="shared" si="11"/>
-        <v>80.069599999999994</v>
-      </c>
-      <c r="AE14" s="154" t="s">
-        <v>135</v>
-      </c>
-      <c r="AF14" s="170">
-        <f t="shared" si="12"/>
-        <v>16</v>
-      </c>
-      <c r="AH14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI14" s="20">
-        <v>197.92</v>
-      </c>
-      <c r="AJ14" s="16">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="15" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B15" s="184" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="133">
-        <v>2</v>
-      </c>
-      <c r="D15" s="133">
-        <v>246.48</v>
-      </c>
-      <c r="E15" s="133">
-        <v>1</v>
-      </c>
-      <c r="F15" s="154">
-        <f t="shared" si="7"/>
-        <v>492.96</v>
-      </c>
-      <c r="G15" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" s="155">
-        <f>E15*20</f>
-        <v>20</v>
-      </c>
-      <c r="J15" s="184" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" s="133">
-        <v>2</v>
-      </c>
-      <c r="L15" s="133">
-        <v>246.48</v>
-      </c>
-      <c r="M15" s="133">
-        <v>1</v>
-      </c>
-      <c r="N15" s="154">
-        <f t="shared" si="8"/>
-        <v>492.96</v>
-      </c>
-      <c r="O15" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="P15" s="155">
-        <f t="shared" si="9"/>
-        <v>20</v>
-      </c>
-      <c r="R15" s="184" t="s">
+      <c r="R15" s="180" t="s">
         <v>108</v>
       </c>
       <c r="S15" s="133">
@@ -30318,88 +30312,88 @@
       <c r="U15" s="133">
         <v>1</v>
       </c>
-      <c r="V15" s="154">
-        <f t="shared" ref="V15:V17" si="13">(T15*1000)/(1000/(S15*U15))</f>
+      <c r="V15" s="153">
+        <f t="shared" ref="V15:V17" si="14">(T15*1000)/(1000/(S15*U15))</f>
         <v>492.96</v>
       </c>
-      <c r="W15" s="154" t="s">
+      <c r="W15" s="153" t="s">
         <v>136</v>
       </c>
-      <c r="X15" s="170">
+      <c r="X15" s="167">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="Z15" s="180" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA15" s="133">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="133">
+        <v>246.48</v>
+      </c>
+      <c r="AC15" s="133">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="153">
+        <f t="shared" si="12"/>
+        <v>492.96</v>
+      </c>
+      <c r="AE15" s="153" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF15" s="167">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="AH15" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI15" s="20">
+        <v>61.83</v>
+      </c>
+      <c r="AJ15" s="16">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="B16" s="181" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="133">
+        <v>1</v>
+      </c>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133">
+        <v>1</v>
+      </c>
+      <c r="F16" s="153"/>
+      <c r="G16" s="153" t="s">
+        <v>137</v>
+      </c>
+      <c r="H16" s="154">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="J16" s="181" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="133">
+        <v>1</v>
+      </c>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133">
+        <v>1</v>
+      </c>
+      <c r="N16" s="153"/>
+      <c r="O16" s="153" t="s">
+        <v>137</v>
+      </c>
+      <c r="P16" s="154">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="Z15" s="184" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA15" s="133">
-        <v>2</v>
-      </c>
-      <c r="AB15" s="133">
-        <v>246.48</v>
-      </c>
-      <c r="AC15" s="133">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="154">
-        <f t="shared" si="11"/>
-        <v>492.96</v>
-      </c>
-      <c r="AE15" s="154" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF15" s="170">
-        <f t="shared" si="12"/>
-        <v>20</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI15" s="20">
-        <v>61.83</v>
-      </c>
-      <c r="AJ15" s="16">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:36" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B16" s="185" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="133">
-        <v>1</v>
-      </c>
-      <c r="D16" s="133"/>
-      <c r="E16" s="133">
-        <v>1</v>
-      </c>
-      <c r="F16" s="154"/>
-      <c r="G16" s="154" t="s">
-        <v>137</v>
-      </c>
-      <c r="H16" s="155">
-        <f>E16*20</f>
-        <v>20</v>
-      </c>
-      <c r="J16" s="185" t="s">
-        <v>7</v>
-      </c>
-      <c r="K16" s="133">
-        <v>1</v>
-      </c>
-      <c r="L16" s="133"/>
-      <c r="M16" s="133">
-        <v>1</v>
-      </c>
-      <c r="N16" s="154"/>
-      <c r="O16" s="154" t="s">
-        <v>137</v>
-      </c>
-      <c r="P16" s="155">
-        <f t="shared" si="9"/>
-        <v>20</v>
-      </c>
-      <c r="R16" s="185" t="s">
+      <c r="R16" s="181" t="s">
         <v>7</v>
       </c>
       <c r="S16" s="133">
@@ -30409,128 +30403,128 @@
       <c r="U16" s="133">
         <v>1</v>
       </c>
-      <c r="V16" s="154">
+      <c r="V16" s="153">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="153" t="s">
+        <v>137</v>
+      </c>
+      <c r="X16" s="167">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="Z16" s="181" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA16" s="133">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="133"/>
+      <c r="AC16" s="133">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="153"/>
+      <c r="AE16" s="153" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF16" s="167">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="154" t="s">
-        <v>137</v>
-      </c>
-      <c r="X16" s="170">
+        <v>20</v>
+      </c>
+      <c r="AH16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI16" s="15">
+        <v>287.60000000000002</v>
+      </c>
+      <c r="AJ16" s="16">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="17" spans="2:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="182" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="155">
+        <v>1</v>
+      </c>
+      <c r="D17" s="155"/>
+      <c r="E17" s="155">
+        <v>1</v>
+      </c>
+      <c r="F17" s="156">
+        <f t="shared" ref="F17" si="15">(D17*1000)/(1000/(C17*E17))</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="156" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="157">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="J17" s="182" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="155">
+        <v>1</v>
+      </c>
+      <c r="L17" s="155"/>
+      <c r="M17" s="155">
+        <v>1</v>
+      </c>
+      <c r="N17" s="156">
+        <f t="shared" ref="N17" si="16">(L17*1000)/(1000/(K17*M17))</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="156" t="s">
+        <v>138</v>
+      </c>
+      <c r="P17" s="157">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="Z16" s="185" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA16" s="133">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="133"/>
-      <c r="AC16" s="133">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="154"/>
-      <c r="AE16" s="154" t="s">
-        <v>137</v>
-      </c>
-      <c r="AF16" s="170">
-        <f t="shared" si="12"/>
+      <c r="R17" s="182" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="155">
+        <v>1</v>
+      </c>
+      <c r="T17" s="155"/>
+      <c r="U17" s="155">
+        <v>1</v>
+      </c>
+      <c r="V17" s="156">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="156" t="s">
+        <v>138</v>
+      </c>
+      <c r="X17" s="168">
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="AH16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI16" s="15">
-        <v>287.60000000000002</v>
-      </c>
-      <c r="AJ16" s="16">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="186" t="s">
+      <c r="Z17" s="182" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="156">
-        <v>1</v>
-      </c>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156">
-        <v>1</v>
-      </c>
-      <c r="F17" s="157">
-        <f t="shared" ref="F17" si="14">(D17*1000)/(1000/(C17*E17))</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="157" t="s">
+      <c r="AA17" s="155">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="155"/>
+      <c r="AC17" s="155">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="156">
+        <f t="shared" ref="AD17" si="17">(AB17*1000)/(1000/(AA17*AC17))</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="158">
-        <f>E17*20</f>
-        <v>20</v>
-      </c>
-      <c r="J17" s="186" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="156">
-        <v>1</v>
-      </c>
-      <c r="L17" s="156"/>
-      <c r="M17" s="156">
-        <v>1</v>
-      </c>
-      <c r="N17" s="157">
-        <f t="shared" ref="N17" si="15">(L17*1000)/(1000/(K17*M17))</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="157" t="s">
-        <v>138</v>
-      </c>
-      <c r="P17" s="158">
-        <f t="shared" si="9"/>
-        <v>20</v>
-      </c>
-      <c r="R17" s="186" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="156">
-        <v>1</v>
-      </c>
-      <c r="T17" s="156"/>
-      <c r="U17" s="156">
-        <v>1</v>
-      </c>
-      <c r="V17" s="157">
+      <c r="AF17" s="168">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="157" t="s">
-        <v>138</v>
-      </c>
-      <c r="X17" s="171">
-        <f t="shared" si="10"/>
-        <v>20</v>
-      </c>
-      <c r="Z17" s="186" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA17" s="156">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="156"/>
-      <c r="AC17" s="156">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="157">
-        <f t="shared" ref="AD17" si="16">(AB17*1000)/(1000/(AA17*AC17))</f>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="157" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF17" s="171">
-        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="AH17" s="14" t="s">
@@ -30544,13 +30538,13 @@
       </c>
     </row>
     <row r="18" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="187"/>
+      <c r="B18" s="183"/>
       <c r="F18" s="32"/>
-      <c r="J18" s="187"/>
+      <c r="J18" s="183"/>
       <c r="N18" s="32"/>
-      <c r="R18" s="187"/>
+      <c r="R18" s="183"/>
       <c r="V18" s="32"/>
-      <c r="Z18" s="187"/>
+      <c r="Z18" s="183"/>
       <c r="AD18" s="32"/>
       <c r="AH18" s="17" t="s">
         <v>28</v>
@@ -30563,7 +30557,7 @@
       </c>
     </row>
     <row r="19" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="188" t="s">
+      <c r="B19" s="184" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="43"/>
@@ -30572,7 +30566,7 @@
       <c r="F19" s="54"/>
       <c r="G19" s="123"/>
       <c r="H19" s="3"/>
-      <c r="J19" s="188" t="s">
+      <c r="J19" s="184" t="s">
         <v>9</v>
       </c>
       <c r="K19" s="43"/>
@@ -30581,7 +30575,7 @@
       <c r="N19" s="54"/>
       <c r="O19" s="123"/>
       <c r="P19" s="3"/>
-      <c r="R19" s="188" t="s">
+      <c r="R19" s="184" t="s">
         <v>9</v>
       </c>
       <c r="S19" s="43"/>
@@ -30590,7 +30584,7 @@
       <c r="V19" s="54"/>
       <c r="W19" s="123"/>
       <c r="X19" s="3"/>
-      <c r="Z19" s="188" t="s">
+      <c r="Z19" s="184" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="43"/>
@@ -30604,7 +30598,7 @@
       <c r="AJ19" s="20"/>
     </row>
     <row r="20" spans="2:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="189" t="s">
+      <c r="B20" s="185" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="47" t="s">
@@ -30621,7 +30615,7 @@
       </c>
       <c r="G20" s="123"/>
       <c r="H20" s="3"/>
-      <c r="J20" s="189" t="s">
+      <c r="J20" s="185" t="s">
         <v>10</v>
       </c>
       <c r="K20" s="47" t="s">
@@ -30638,7 +30632,7 @@
       </c>
       <c r="O20" s="123"/>
       <c r="P20" s="3"/>
-      <c r="R20" s="189" t="s">
+      <c r="R20" s="185" t="s">
         <v>10</v>
       </c>
       <c r="S20" s="47" t="s">
@@ -30655,7 +30649,7 @@
       </c>
       <c r="W20" s="123"/>
       <c r="X20" s="3"/>
-      <c r="Z20" s="189" t="s">
+      <c r="Z20" s="185" t="s">
         <v>10</v>
       </c>
       <c r="AA20" s="47" t="s">
@@ -30679,8 +30673,8 @@
       <c r="AJ20" s="76"/>
     </row>
     <row r="21" spans="2:36" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="190" t="s">
-        <v>150</v>
+      <c r="B21" s="186" t="s">
+        <v>149</v>
       </c>
       <c r="C21" s="51">
         <f>C6</f>
@@ -30694,13 +30688,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="52">
-        <f t="shared" ref="F21:F34" si="17">IF(OR(C21=0, E21=0), 0, (D21*1000)/(1000/(C21*E21)))</f>
+        <f t="shared" ref="F21:F34" si="18">IF(OR(C21=0, E21=0), 0, (D21*1000)/(1000/(C21*E21)))</f>
         <v>0</v>
       </c>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
-      <c r="J21" s="190" t="s">
-        <v>150</v>
+      <c r="J21" s="186" t="s">
+        <v>149</v>
       </c>
       <c r="K21" s="51">
         <f>K6</f>
@@ -30719,8 +30713,8 @@
       </c>
       <c r="O21" s="35"/>
       <c r="P21" s="35"/>
-      <c r="R21" s="190" t="s">
-        <v>150</v>
+      <c r="R21" s="186" t="s">
+        <v>149</v>
       </c>
       <c r="S21" s="51">
         <f>S6</f>
@@ -30739,8 +30733,8 @@
       </c>
       <c r="W21" s="35"/>
       <c r="X21" s="35"/>
-      <c r="Z21" s="190" t="s">
-        <v>150</v>
+      <c r="Z21" s="186" t="s">
+        <v>149</v>
       </c>
       <c r="AA21" s="51">
         <f>AA6</f>
@@ -30770,8 +30764,8 @@
       </c>
     </row>
     <row r="22" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B22" s="191" t="s">
-        <v>151</v>
+      <c r="B22" s="187" t="s">
+        <v>150</v>
       </c>
       <c r="C22" s="22">
         <f>C6</f>
@@ -30785,13 +30779,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
-      <c r="J22" s="191" t="s">
-        <v>151</v>
+      <c r="J22" s="187" t="s">
+        <v>150</v>
       </c>
       <c r="K22" s="22">
         <f>K6</f>
@@ -30805,13 +30799,13 @@
         <v>0.5</v>
       </c>
       <c r="N22" s="33">
-        <f t="shared" ref="N22:N34" si="18">IF(OR(K22=0, M22=0), 0, (L22*1000)/(1000/(K22*M22)))</f>
+        <f t="shared" ref="N22:N34" si="19">IF(OR(K22=0, M22=0), 0, (L22*1000)/(1000/(K22*M22)))</f>
         <v>15.48685</v>
       </c>
       <c r="O22" s="35"/>
       <c r="P22" s="35"/>
-      <c r="R22" s="191" t="s">
-        <v>151</v>
+      <c r="R22" s="187" t="s">
+        <v>150</v>
       </c>
       <c r="S22" s="22">
         <f>S6</f>
@@ -30825,13 +30819,13 @@
         <v>1</v>
       </c>
       <c r="V22" s="33">
-        <f t="shared" ref="V22:V34" si="19">IF(OR(S22=0,U22=0),0,(T22*1000)/(1000/(S22*U22)))</f>
+        <f t="shared" ref="V22:V34" si="20">IF(OR(S22=0,U22=0),0,(T22*1000)/(1000/(S22*U22)))</f>
         <v>30.973700000000001</v>
       </c>
       <c r="W22" s="35"/>
       <c r="X22" s="35"/>
-      <c r="Z22" s="191" t="s">
-        <v>151</v>
+      <c r="Z22" s="187" t="s">
+        <v>150</v>
       </c>
       <c r="AA22" s="22">
         <f>AA6</f>
@@ -30845,7 +30839,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="33">
-        <f t="shared" ref="AD22:AD34" si="20">IF(OR(AA22=0,AC22=0),0,(AB22*1000)/(1000/(AA22*AC22)))</f>
+        <f t="shared" ref="AD22:AD34" si="21">IF(OR(AA22=0,AC22=0),0,(AB22*1000)/(1000/(AA22*AC22)))</f>
         <v>61.947400000000002</v>
       </c>
       <c r="AE22" s="35"/>
@@ -30859,8 +30853,8 @@
       <c r="AJ22" s="79"/>
     </row>
     <row r="23" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B23" s="192" t="s">
-        <v>152</v>
+      <c r="B23" s="188" t="s">
+        <v>151</v>
       </c>
       <c r="C23" s="22">
         <f>C7</f>
@@ -30874,13 +30868,13 @@
         <v>2</v>
       </c>
       <c r="F23" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>156.37719999999999</v>
       </c>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
-      <c r="J23" s="192" t="s">
-        <v>152</v>
+      <c r="J23" s="188" t="s">
+        <v>151</v>
       </c>
       <c r="K23" s="22">
         <f>K7</f>
@@ -30894,13 +30888,13 @@
         <v>2</v>
       </c>
       <c r="N23" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>156.37719999999999</v>
       </c>
       <c r="O23" s="35"/>
       <c r="P23" s="35"/>
-      <c r="R23" s="192" t="s">
-        <v>152</v>
+      <c r="R23" s="188" t="s">
+        <v>151</v>
       </c>
       <c r="S23" s="22">
         <f>S7</f>
@@ -30914,13 +30908,13 @@
         <v>2</v>
       </c>
       <c r="V23" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>156.37719999999999</v>
       </c>
       <c r="W23" s="35"/>
       <c r="X23" s="35"/>
-      <c r="Z23" s="192" t="s">
-        <v>152</v>
+      <c r="Z23" s="188" t="s">
+        <v>151</v>
       </c>
       <c r="AA23" s="22">
         <f>AA7</f>
@@ -30934,7 +30928,7 @@
         <v>2</v>
       </c>
       <c r="AD23" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>156.37719999999999</v>
       </c>
       <c r="AE23" s="35"/>
@@ -30950,8 +30944,8 @@
       </c>
     </row>
     <row r="24" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B24" s="192" t="s">
-        <v>153</v>
+      <c r="B24" s="188" t="s">
+        <v>152</v>
       </c>
       <c r="C24" s="22">
         <f>C7</f>
@@ -30965,13 +30959,13 @@
         <v>2</v>
       </c>
       <c r="F24" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>56.024000000000001</v>
       </c>
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
-      <c r="J24" s="192" t="s">
-        <v>153</v>
+      <c r="J24" s="188" t="s">
+        <v>152</v>
       </c>
       <c r="K24" s="22">
         <f>K7</f>
@@ -30985,13 +30979,13 @@
         <v>2</v>
       </c>
       <c r="N24" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>56.024000000000001</v>
       </c>
       <c r="O24" s="35"/>
       <c r="P24" s="35"/>
-      <c r="R24" s="192" t="s">
-        <v>153</v>
+      <c r="R24" s="188" t="s">
+        <v>152</v>
       </c>
       <c r="S24" s="22">
         <f>S7</f>
@@ -31005,13 +30999,13 @@
         <v>2</v>
       </c>
       <c r="V24" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>56.024000000000001</v>
       </c>
       <c r="W24" s="35"/>
       <c r="X24" s="35"/>
-      <c r="Z24" s="192" t="s">
-        <v>153</v>
+      <c r="Z24" s="188" t="s">
+        <v>152</v>
       </c>
       <c r="AA24" s="22">
         <f>AA7</f>
@@ -31025,7 +31019,7 @@
         <v>2</v>
       </c>
       <c r="AD24" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>56.024000000000001</v>
       </c>
       <c r="AE24" s="35"/>
@@ -31041,8 +31035,8 @@
       </c>
     </row>
     <row r="25" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B25" s="193" t="s">
-        <v>154</v>
+      <c r="B25" s="189" t="s">
+        <v>153</v>
       </c>
       <c r="C25" s="22">
         <f>C8</f>
@@ -31056,13 +31050,13 @@
         <v>2</v>
       </c>
       <c r="F25" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>160.31200000000001</v>
       </c>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
-      <c r="J25" s="193" t="s">
-        <v>154</v>
+      <c r="J25" s="189" t="s">
+        <v>153</v>
       </c>
       <c r="K25" s="22">
         <f>K8</f>
@@ -31076,13 +31070,13 @@
         <v>1.75</v>
       </c>
       <c r="N25" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>140.273</v>
       </c>
       <c r="O25" s="35"/>
       <c r="P25" s="35"/>
-      <c r="R25" s="193" t="s">
-        <v>154</v>
+      <c r="R25" s="189" t="s">
+        <v>153</v>
       </c>
       <c r="S25" s="22">
         <f>S8</f>
@@ -31096,13 +31090,13 @@
         <v>1.5</v>
       </c>
       <c r="V25" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>120.23400000000001</v>
       </c>
       <c r="W25" s="35"/>
       <c r="X25" s="35"/>
-      <c r="Z25" s="193" t="s">
-        <v>154</v>
+      <c r="Z25" s="189" t="s">
+        <v>153</v>
       </c>
       <c r="AA25" s="22">
         <f>AA8</f>
@@ -31116,7 +31110,7 @@
         <v>1.6</v>
       </c>
       <c r="AD25" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>128.24959999999999</v>
       </c>
       <c r="AE25" s="35"/>
@@ -31132,8 +31126,8 @@
       </c>
     </row>
     <row r="26" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B26" s="193" t="s">
-        <v>155</v>
+      <c r="B26" s="189" t="s">
+        <v>154</v>
       </c>
       <c r="C26" s="22">
         <f>C8</f>
@@ -31147,13 +31141,13 @@
         <v>2</v>
       </c>
       <c r="F26" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>112.048</v>
       </c>
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
-      <c r="J26" s="193" t="s">
-        <v>155</v>
+      <c r="J26" s="189" t="s">
+        <v>154</v>
       </c>
       <c r="K26" s="22">
         <f>K8</f>
@@ -31167,13 +31161,13 @@
         <v>1.75</v>
       </c>
       <c r="N26" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>98.042000000000002</v>
       </c>
       <c r="O26" s="35"/>
       <c r="P26" s="35"/>
-      <c r="R26" s="193" t="s">
-        <v>155</v>
+      <c r="R26" s="189" t="s">
+        <v>154</v>
       </c>
       <c r="S26" s="22">
         <f>S8</f>
@@ -31187,13 +31181,13 @@
         <v>1.5</v>
       </c>
       <c r="V26" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>84.036000000000001</v>
       </c>
       <c r="W26" s="35"/>
       <c r="X26" s="35"/>
-      <c r="Z26" s="193" t="s">
-        <v>155</v>
+      <c r="Z26" s="189" t="s">
+        <v>154</v>
       </c>
       <c r="AA26" s="22">
         <f>AA8</f>
@@ -31207,7 +31201,7 @@
         <v>1.6</v>
       </c>
       <c r="AD26" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>89.638400000000004</v>
       </c>
       <c r="AE26" s="35"/>
@@ -31217,8 +31211,8 @@
       <c r="AJ26" s="11"/>
     </row>
     <row r="27" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B27" s="194" t="s">
-        <v>156</v>
+      <c r="B27" s="190" t="s">
+        <v>155</v>
       </c>
       <c r="C27" s="22">
         <f>C9</f>
@@ -31237,8 +31231,8 @@
       </c>
       <c r="G27" s="35"/>
       <c r="H27" s="35"/>
-      <c r="J27" s="194" t="s">
-        <v>156</v>
+      <c r="J27" s="190" t="s">
+        <v>155</v>
       </c>
       <c r="K27" s="22">
         <f>K9</f>
@@ -31252,13 +31246,13 @@
         <v>1.75</v>
       </c>
       <c r="N27" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>49.021000000000001</v>
       </c>
       <c r="O27" s="35"/>
       <c r="P27" s="35"/>
-      <c r="R27" s="194" t="s">
-        <v>156</v>
+      <c r="R27" s="190" t="s">
+        <v>155</v>
       </c>
       <c r="S27" s="22">
         <f>S9</f>
@@ -31272,13 +31266,13 @@
         <v>2</v>
       </c>
       <c r="V27" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>56.024000000000001</v>
       </c>
       <c r="W27" s="35"/>
       <c r="X27" s="35"/>
-      <c r="Z27" s="194" t="s">
-        <v>156</v>
+      <c r="Z27" s="190" t="s">
+        <v>155</v>
       </c>
       <c r="AA27" s="22">
         <f>AA9</f>
@@ -31308,8 +31302,8 @@
       </c>
     </row>
     <row r="28" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B28" s="195" t="s">
-        <v>157</v>
+      <c r="B28" s="191" t="s">
+        <v>156</v>
       </c>
       <c r="C28" s="22">
         <f>C12</f>
@@ -31323,13 +31317,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G28" s="35"/>
       <c r="H28" s="35"/>
-      <c r="J28" s="195" t="s">
-        <v>157</v>
+      <c r="J28" s="191" t="s">
+        <v>156</v>
       </c>
       <c r="K28" s="22">
         <f>K12</f>
@@ -31343,13 +31337,13 @@
         <v>0</v>
       </c>
       <c r="N28" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O28" s="35"/>
       <c r="P28" s="35"/>
-      <c r="R28" s="195" t="s">
-        <v>157</v>
+      <c r="R28" s="191" t="s">
+        <v>156</v>
       </c>
       <c r="S28" s="22">
         <f>S12</f>
@@ -31363,13 +31357,13 @@
         <v>0</v>
       </c>
       <c r="V28" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W28" s="35"/>
       <c r="X28" s="35"/>
-      <c r="Z28" s="195" t="s">
-        <v>157</v>
+      <c r="Z28" s="191" t="s">
+        <v>156</v>
       </c>
       <c r="AA28" s="22">
         <f>AA12</f>
@@ -31383,7 +31377,7 @@
         <v>0</v>
       </c>
       <c r="AD28" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE28" s="35"/>
@@ -31399,8 +31393,8 @@
       </c>
     </row>
     <row r="29" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B29" s="195" t="s">
-        <v>158</v>
+      <c r="B29" s="191" t="s">
+        <v>157</v>
       </c>
       <c r="C29" s="22">
         <f>C12</f>
@@ -31414,13 +31408,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G29" s="35"/>
       <c r="H29" s="35"/>
-      <c r="J29" s="195" t="s">
-        <v>158</v>
+      <c r="J29" s="191" t="s">
+        <v>157</v>
       </c>
       <c r="K29" s="22">
         <f>K12</f>
@@ -31434,13 +31428,13 @@
         <v>0</v>
       </c>
       <c r="N29" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O29" s="35"/>
       <c r="P29" s="35"/>
-      <c r="R29" s="195" t="s">
-        <v>158</v>
+      <c r="R29" s="191" t="s">
+        <v>157</v>
       </c>
       <c r="S29" s="22">
         <f>S12</f>
@@ -31454,13 +31448,13 @@
         <v>0</v>
       </c>
       <c r="V29" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W29" s="35"/>
       <c r="X29" s="35"/>
-      <c r="Z29" s="195" t="s">
-        <v>158</v>
+      <c r="Z29" s="191" t="s">
+        <v>157</v>
       </c>
       <c r="AA29" s="22">
         <f>AA12</f>
@@ -31474,7 +31468,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE29" s="35"/>
@@ -31490,7 +31484,7 @@
       </c>
     </row>
     <row r="30" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B30" s="196" t="s">
+      <c r="B30" s="192" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="22">
@@ -31505,12 +31499,12 @@
         <v>0</v>
       </c>
       <c r="F30" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G30" s="35"/>
       <c r="H30" s="35"/>
-      <c r="J30" s="196" t="s">
+      <c r="J30" s="192" t="s">
         <v>11</v>
       </c>
       <c r="K30" s="22">
@@ -31525,12 +31519,12 @@
         <v>0</v>
       </c>
       <c r="N30" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O30" s="35"/>
       <c r="P30" s="35"/>
-      <c r="R30" s="196" t="s">
+      <c r="R30" s="192" t="s">
         <v>11</v>
       </c>
       <c r="S30" s="22">
@@ -31545,12 +31539,12 @@
         <v>0</v>
       </c>
       <c r="V30" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W30" s="35"/>
       <c r="X30" s="35"/>
-      <c r="Z30" s="196" t="s">
+      <c r="Z30" s="192" t="s">
         <v>11</v>
       </c>
       <c r="AA30" s="22">
@@ -31565,7 +31559,7 @@
         <v>0</v>
       </c>
       <c r="AD30" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE30" s="35"/>
@@ -31581,7 +31575,7 @@
       </c>
     </row>
     <row r="31" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B31" s="196" t="s">
+      <c r="B31" s="192" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="22">
@@ -31596,12 +31590,12 @@
         <v>0</v>
       </c>
       <c r="F31" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="G31" s="35"/>
       <c r="H31" s="35"/>
-      <c r="J31" s="196" t="s">
+      <c r="J31" s="192" t="s">
         <v>12</v>
       </c>
       <c r="K31" s="22">
@@ -31616,12 +31610,12 @@
         <v>0</v>
       </c>
       <c r="N31" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="O31" s="35"/>
       <c r="P31" s="35"/>
-      <c r="R31" s="196" t="s">
+      <c r="R31" s="192" t="s">
         <v>12</v>
       </c>
       <c r="S31" s="22">
@@ -31636,12 +31630,12 @@
         <v>0</v>
       </c>
       <c r="V31" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W31" s="35"/>
       <c r="X31" s="35"/>
-      <c r="Z31" s="196" t="s">
+      <c r="Z31" s="192" t="s">
         <v>12</v>
       </c>
       <c r="AA31" s="22">
@@ -31656,7 +31650,7 @@
         <v>0</v>
       </c>
       <c r="AD31" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE31" s="35"/>
@@ -31672,8 +31666,8 @@
       </c>
     </row>
     <row r="32" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B32" s="197" t="s">
-        <v>159</v>
+      <c r="B32" s="193" t="s">
+        <v>158</v>
       </c>
       <c r="C32" s="22">
         <f>C14</f>
@@ -31687,13 +31681,13 @@
         <v>0.04</v>
       </c>
       <c r="F32" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.6031200000000001</v>
       </c>
       <c r="G32" s="35"/>
       <c r="H32" s="35"/>
-      <c r="J32" s="197" t="s">
-        <v>159</v>
+      <c r="J32" s="193" t="s">
+        <v>158</v>
       </c>
       <c r="K32" s="22">
         <f>K14</f>
@@ -31707,13 +31701,13 @@
         <v>0.5</v>
       </c>
       <c r="N32" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>20.039000000000001</v>
       </c>
       <c r="O32" s="35"/>
       <c r="P32" s="35"/>
-      <c r="R32" s="197" t="s">
-        <v>159</v>
+      <c r="R32" s="193" t="s">
+        <v>158</v>
       </c>
       <c r="S32" s="22">
         <f>S14</f>
@@ -31727,13 +31721,13 @@
         <v>1</v>
       </c>
       <c r="V32" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>40.078000000000003</v>
       </c>
       <c r="W32" s="35"/>
       <c r="X32" s="35"/>
-      <c r="Z32" s="197" t="s">
-        <v>159</v>
+      <c r="Z32" s="193" t="s">
+        <v>158</v>
       </c>
       <c r="AA32" s="22">
         <f>AA14</f>
@@ -31747,7 +31741,7 @@
         <v>0.8</v>
       </c>
       <c r="AD32" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>32.062399999999997</v>
       </c>
       <c r="AE32" s="35"/>
@@ -31763,8 +31757,8 @@
       </c>
     </row>
     <row r="33" spans="2:36" ht="18" x14ac:dyDescent="0.35">
-      <c r="B33" s="198" t="s">
-        <v>160</v>
+      <c r="B33" s="194" t="s">
+        <v>159</v>
       </c>
       <c r="C33" s="22">
         <f>C15</f>
@@ -31778,13 +31772,13 @@
         <v>1</v>
       </c>
       <c r="F33" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>48.61</v>
       </c>
       <c r="G33" s="35"/>
       <c r="H33" s="35"/>
-      <c r="J33" s="198" t="s">
-        <v>160</v>
+      <c r="J33" s="194" t="s">
+        <v>159</v>
       </c>
       <c r="K33" s="22">
         <f>K15</f>
@@ -31798,13 +31792,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>48.61</v>
       </c>
       <c r="O33" s="35"/>
       <c r="P33" s="35"/>
-      <c r="R33" s="198" t="s">
-        <v>160</v>
+      <c r="R33" s="194" t="s">
+        <v>159</v>
       </c>
       <c r="S33" s="22">
         <f>S15</f>
@@ -31818,13 +31812,13 @@
         <v>1</v>
       </c>
       <c r="V33" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>48.61</v>
       </c>
       <c r="W33" s="35"/>
       <c r="X33" s="35"/>
-      <c r="Z33" s="198" t="s">
-        <v>160</v>
+      <c r="Z33" s="194" t="s">
+        <v>159</v>
       </c>
       <c r="AA33" s="22">
         <f>AA15</f>
@@ -31838,7 +31832,7 @@
         <v>1</v>
       </c>
       <c r="AD33" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>48.61</v>
       </c>
       <c r="AE33" s="35"/>
@@ -31848,8 +31842,8 @@
       <c r="AJ33" s="11"/>
     </row>
     <row r="34" spans="2:36" ht="18.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="198" t="s">
-        <v>161</v>
+      <c r="B34" s="194" t="s">
+        <v>160</v>
       </c>
       <c r="C34" s="22">
         <f>C15</f>
@@ -31863,13 +31857,13 @@
         <v>1</v>
       </c>
       <c r="F34" s="33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>64.13</v>
       </c>
       <c r="G34" s="35"/>
       <c r="H34" s="35"/>
-      <c r="J34" s="198" t="s">
-        <v>161</v>
+      <c r="J34" s="194" t="s">
+        <v>160</v>
       </c>
       <c r="K34" s="22">
         <f>K15</f>
@@ -31883,13 +31877,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>64.13</v>
       </c>
       <c r="O34" s="35"/>
       <c r="P34" s="35"/>
-      <c r="R34" s="198" t="s">
-        <v>161</v>
+      <c r="R34" s="194" t="s">
+        <v>160</v>
       </c>
       <c r="S34" s="22">
         <f>S15</f>
@@ -31903,13 +31897,13 @@
         <v>1</v>
       </c>
       <c r="V34" s="33">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>64.13</v>
       </c>
       <c r="W34" s="35"/>
       <c r="X34" s="35"/>
-      <c r="Z34" s="198" t="s">
-        <v>161</v>
+      <c r="Z34" s="194" t="s">
+        <v>160</v>
       </c>
       <c r="AA34" s="22">
         <f>AA15</f>
@@ -31923,7 +31917,7 @@
         <v>1</v>
       </c>
       <c r="AD34" s="33">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>64.13</v>
       </c>
       <c r="AE34" s="35"/>
@@ -31937,25 +31931,25 @@
       <c r="AJ34" s="6"/>
     </row>
     <row r="35" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="187"/>
+      <c r="B35" s="183"/>
       <c r="F35" s="34"/>
       <c r="G35" s="35"/>
       <c r="H35" s="35"/>
-      <c r="J35" s="187"/>
+      <c r="J35" s="183"/>
       <c r="N35" s="34"/>
       <c r="O35" s="35"/>
       <c r="P35" s="35"/>
-      <c r="R35" s="187"/>
+      <c r="R35" s="183"/>
       <c r="V35" s="34"/>
       <c r="W35" s="35"/>
       <c r="X35" s="35"/>
-      <c r="Z35" s="187"/>
+      <c r="Z35" s="183"/>
       <c r="AD35" s="34"/>
       <c r="AE35" s="35"/>
       <c r="AF35" s="35"/>
     </row>
     <row r="36" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B36" s="188" t="s">
+      <c r="B36" s="184" t="s">
         <v>13</v>
       </c>
       <c r="C36" s="43"/>
@@ -31964,7 +31958,7 @@
       <c r="F36" s="45"/>
       <c r="G36" s="124"/>
       <c r="H36" s="124"/>
-      <c r="J36" s="188" t="s">
+      <c r="J36" s="184" t="s">
         <v>13</v>
       </c>
       <c r="K36" s="43"/>
@@ -31973,7 +31967,7 @@
       <c r="N36" s="50"/>
       <c r="O36" s="124"/>
       <c r="P36" s="125"/>
-      <c r="R36" s="188" t="s">
+      <c r="R36" s="184" t="s">
         <v>13</v>
       </c>
       <c r="S36" s="43"/>
@@ -31982,7 +31976,7 @@
       <c r="V36" s="50"/>
       <c r="W36" s="125"/>
       <c r="X36" s="125"/>
-      <c r="Z36" s="188" t="s">
+      <c r="Z36" s="184" t="s">
         <v>13</v>
       </c>
       <c r="AA36" s="43"/>
@@ -31993,7 +31987,7 @@
       <c r="AF36" s="125"/>
     </row>
     <row r="37" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="189" t="s">
+      <c r="B37" s="185" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="47" t="s">
@@ -32008,7 +32002,7 @@
       </c>
       <c r="G37" s="138"/>
       <c r="H37" s="125"/>
-      <c r="J37" s="189" t="s">
+      <c r="J37" s="185" t="s">
         <v>14</v>
       </c>
       <c r="K37" s="47" t="s">
@@ -32023,7 +32017,7 @@
       </c>
       <c r="O37" s="138"/>
       <c r="P37" s="125"/>
-      <c r="R37" s="189" t="s">
+      <c r="R37" s="185" t="s">
         <v>14</v>
       </c>
       <c r="S37" s="47" t="s">
@@ -32038,7 +32032,7 @@
       </c>
       <c r="W37" s="138"/>
       <c r="X37" s="125"/>
-      <c r="Z37" s="189" t="s">
+      <c r="Z37" s="185" t="s">
         <v>14</v>
       </c>
       <c r="AA37" s="47" t="s">
@@ -32055,7 +32049,7 @@
       <c r="AF37" s="125"/>
     </row>
     <row r="38" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B38" s="199" t="s">
+      <c r="B38" s="113" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="120">
@@ -32070,7 +32064,7 @@
       <c r="F38" s="32">
         <v>6.7</v>
       </c>
-      <c r="J38" s="199" t="s">
+      <c r="J38" s="113" t="s">
         <v>15</v>
       </c>
       <c r="K38" s="120">
@@ -32078,13 +32072,13 @@
         <v>210.09000000000003</v>
       </c>
       <c r="M38" s="35">
-        <f>C47-K38</f>
+        <f t="shared" ref="M38:M43" si="22">C47-K38</f>
         <v>0</v>
       </c>
       <c r="N38" s="32">
         <v>6.79</v>
       </c>
-      <c r="R38" s="199" t="s">
+      <c r="R38" s="113" t="s">
         <v>15</v>
       </c>
       <c r="S38" s="59">
@@ -32092,13 +32086,13 @@
         <v>210.09</v>
       </c>
       <c r="U38" s="118">
-        <f>S38-C47</f>
+        <f t="shared" ref="U38:U43" si="23">S38-C47</f>
         <v>0</v>
       </c>
       <c r="V38" s="32">
         <v>6.7</v>
       </c>
-      <c r="Z38" s="199" t="s">
+      <c r="Z38" s="113" t="s">
         <v>15</v>
       </c>
       <c r="AA38" s="59">
@@ -32106,7 +32100,7 @@
         <v>210.09</v>
       </c>
       <c r="AC38" s="35">
-        <f>C47-AA38</f>
+        <f t="shared" ref="AC38:AC43" si="24">C47-AA38</f>
         <v>0</v>
       </c>
       <c r="AD38" s="32">
@@ -32114,7 +32108,7 @@
       </c>
     </row>
     <row r="39" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B39" s="200" t="s">
+      <c r="B39" s="114" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="22">
@@ -32122,11 +32116,11 @@
         <v>0</v>
       </c>
       <c r="E39" s="35">
-        <f t="shared" ref="E39:E43" si="21">C48-C39</f>
+        <f t="shared" ref="E39:E43" si="25">C48-C39</f>
         <v>30.973700000000001</v>
       </c>
       <c r="F39" s="32"/>
-      <c r="J39" s="200" t="s">
+      <c r="J39" s="114" t="s">
         <v>16</v>
       </c>
       <c r="K39" s="131">
@@ -32134,11 +32128,11 @@
         <v>15.48685</v>
       </c>
       <c r="M39" s="35">
-        <f>C48-K39</f>
+        <f t="shared" si="22"/>
         <v>15.48685</v>
       </c>
       <c r="N39" s="32"/>
-      <c r="R39" s="200" t="s">
+      <c r="R39" s="114" t="s">
         <v>16</v>
       </c>
       <c r="S39" s="22">
@@ -32146,11 +32140,11 @@
         <v>30.973700000000001</v>
       </c>
       <c r="U39" s="118">
-        <f>S39-C48</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V39" s="32"/>
-      <c r="Z39" s="200" t="s">
+      <c r="Z39" s="114" t="s">
         <v>16</v>
       </c>
       <c r="AA39" s="22">
@@ -32158,13 +32152,13 @@
         <v>61.947400000000002</v>
       </c>
       <c r="AC39" s="35">
-        <f>C48-AA39</f>
+        <f t="shared" si="24"/>
         <v>-30.973700000000001</v>
       </c>
       <c r="AD39" s="32"/>
     </row>
     <row r="40" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B40" s="200" t="s">
+      <c r="B40" s="114" t="s">
         <v>17</v>
       </c>
       <c r="C40" s="119">
@@ -32172,11 +32166,11 @@
         <v>156.37719999999999</v>
       </c>
       <c r="E40" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F40" s="32"/>
-      <c r="J40" s="200" t="s">
+      <c r="J40" s="114" t="s">
         <v>17</v>
       </c>
       <c r="K40" s="57">
@@ -32184,11 +32178,11 @@
         <v>156.37719999999999</v>
       </c>
       <c r="M40" s="35">
-        <f>C49-K40</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N40" s="32"/>
-      <c r="R40" s="200" t="s">
+      <c r="R40" s="114" t="s">
         <v>17</v>
       </c>
       <c r="S40" s="57">
@@ -32196,11 +32190,11 @@
         <v>156.37719999999999</v>
       </c>
       <c r="U40" s="118">
-        <f>S40-C49</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V40" s="32"/>
-      <c r="Z40" s="200" t="s">
+      <c r="Z40" s="114" t="s">
         <v>17</v>
       </c>
       <c r="AA40" s="57">
@@ -32208,13 +32202,13 @@
         <v>156.37719999999999</v>
       </c>
       <c r="AC40" s="35">
-        <f>C49-AA40</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD40" s="32"/>
     </row>
     <row r="41" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B41" s="200" t="s">
+      <c r="B41" s="114" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="119">
@@ -32222,11 +32216,11 @@
         <v>161.91512</v>
       </c>
       <c r="E41" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>-1.6031199999999899</v>
       </c>
       <c r="F41" s="32"/>
-      <c r="J41" s="200" t="s">
+      <c r="J41" s="114" t="s">
         <v>18</v>
       </c>
       <c r="K41" s="57">
@@ -32234,11 +32228,11 @@
         <v>160.31200000000001</v>
       </c>
       <c r="M41" s="35">
-        <f>C50-K41</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N41" s="32"/>
-      <c r="R41" s="200" t="s">
+      <c r="R41" s="114" t="s">
         <v>18</v>
       </c>
       <c r="S41" s="57">
@@ -32246,11 +32240,11 @@
         <v>160.31200000000001</v>
       </c>
       <c r="U41" s="118">
-        <f>S41-C50</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V41" s="32"/>
-      <c r="Z41" s="200" t="s">
+      <c r="Z41" s="114" t="s">
         <v>18</v>
       </c>
       <c r="AA41" s="57">
@@ -32258,13 +32252,13 @@
         <v>160.31199999999998</v>
       </c>
       <c r="AC41" s="35">
-        <f>C50-AA41</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD41" s="32"/>
     </row>
     <row r="42" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B42" s="200" t="s">
+      <c r="B42" s="114" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="57">
@@ -32272,11 +32266,11 @@
         <v>48.61</v>
       </c>
       <c r="E42" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F42" s="32"/>
-      <c r="J42" s="200" t="s">
+      <c r="J42" s="114" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="57">
@@ -32284,11 +32278,11 @@
         <v>48.61</v>
       </c>
       <c r="M42" s="35">
-        <f>C51-K42</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N42" s="32"/>
-      <c r="R42" s="200" t="s">
+      <c r="R42" s="114" t="s">
         <v>19</v>
       </c>
       <c r="S42" s="57">
@@ -32296,11 +32290,11 @@
         <v>48.61</v>
       </c>
       <c r="U42" s="118">
-        <f>S42-C51</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V42" s="32"/>
-      <c r="Z42" s="200" t="s">
+      <c r="Z42" s="114" t="s">
         <v>19</v>
       </c>
       <c r="AA42" s="57">
@@ -32308,13 +32302,13 @@
         <v>48.61</v>
       </c>
       <c r="AC42" s="35">
-        <f>C51-AA42</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD42" s="32"/>
     </row>
     <row r="43" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="201" t="s">
+      <c r="B43" s="115" t="s">
         <v>20</v>
       </c>
       <c r="C43" s="58">
@@ -32323,11 +32317,11 @@
       </c>
       <c r="D43" s="36"/>
       <c r="E43" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F43" s="38"/>
-      <c r="J43" s="201" t="s">
+      <c r="J43" s="115" t="s">
         <v>20</v>
       </c>
       <c r="K43" s="58">
@@ -32336,11 +32330,11 @@
       </c>
       <c r="L43" s="36"/>
       <c r="M43" s="35">
-        <f>C52-K43</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N43" s="38"/>
-      <c r="R43" s="201" t="s">
+      <c r="R43" s="115" t="s">
         <v>20</v>
       </c>
       <c r="S43" s="58">
@@ -32349,11 +32343,11 @@
       </c>
       <c r="T43" s="36"/>
       <c r="U43" s="118">
-        <f>S43-C52</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="V43" s="38"/>
-      <c r="Z43" s="201" t="s">
+      <c r="Z43" s="115" t="s">
         <v>20</v>
       </c>
       <c r="AA43" s="58">
@@ -32362,13 +32356,13 @@
       </c>
       <c r="AB43" s="36"/>
       <c r="AC43" s="35">
-        <f>C52-AA43</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD43" s="38"/>
     </row>
     <row r="45" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="R45" s="172" t="s">
+      <c r="R45" t="s">
         <v>139</v>
       </c>
       <c r="S45" t="s">
@@ -32379,7 +32373,7 @@
       <c r="B46" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="R46" s="172" t="s">
+      <c r="R46" t="s">
         <v>15</v>
       </c>
       <c r="S46">
@@ -32391,13 +32385,13 @@
       </c>
     </row>
     <row r="47" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B47" s="172" t="s">
+      <c r="B47" t="s">
         <v>15</v>
       </c>
       <c r="C47">
         <v>210.09</v>
       </c>
-      <c r="R47" s="172" t="s">
+      <c r="R47" t="s">
         <v>16</v>
       </c>
       <c r="S47">
@@ -32409,79 +32403,79 @@
       </c>
     </row>
     <row r="48" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B48" s="172" t="s">
+      <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48">
         <v>30.973700000000001</v>
       </c>
-      <c r="R48" s="172" t="s">
+      <c r="R48" t="s">
         <v>17</v>
       </c>
       <c r="S48">
         <v>151.27000000000001</v>
       </c>
       <c r="U48">
-        <f t="shared" ref="U48:U51" si="22">S40-S48</f>
+        <f t="shared" ref="U48:U51" si="26">S40-S48</f>
         <v>5.1071999999999775</v>
       </c>
     </row>
     <row r="49" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B49" s="172" t="s">
+      <c r="B49" t="s">
         <v>17</v>
       </c>
       <c r="C49">
         <v>156.37719999999999</v>
       </c>
-      <c r="R49" s="172" t="s">
+      <c r="R49" t="s">
         <v>18</v>
       </c>
       <c r="S49">
         <v>155.08000000000001</v>
       </c>
       <c r="U49">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>5.2319999999999993</v>
       </c>
     </row>
     <row r="50" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B50" s="172" t="s">
+      <c r="B50" t="s">
         <v>18</v>
       </c>
       <c r="C50">
         <v>160.31200000000001</v>
       </c>
-      <c r="R50" s="172" t="s">
+      <c r="R50" t="s">
         <v>19</v>
       </c>
       <c r="S50">
         <v>47.02</v>
       </c>
       <c r="U50">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>1.5899999999999963</v>
       </c>
     </row>
     <row r="51" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B51" s="172" t="s">
+      <c r="B51" t="s">
         <v>19</v>
       </c>
       <c r="C51">
         <v>48.61</v>
       </c>
-      <c r="R51" s="172" t="s">
+      <c r="R51" t="s">
         <v>20</v>
       </c>
       <c r="S51">
         <v>62.04</v>
       </c>
       <c r="U51">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>2.0899999999999963</v>
       </c>
     </row>
     <row r="52" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B52" s="172" t="s">
+      <c r="B52" t="s">
         <v>20</v>
       </c>
       <c r="C52">
